--- a/important_mails_2026-03-20.xlsx
+++ b/important_mails_2026-03-20.xlsx
@@ -54,9 +54,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -424,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,6 +482,7962 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Disposal order created for unsellable FBA inventory</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated Removals of Unfulfillable Inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Hello,
+You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
+ Why is this happening?
+This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
+ Removal order ID:
+- kpCypnMqWe
+ Unsellable Products:
+- FNSKU: X00265F4H9 Quantity: 1
+- FNSKU: X002C17O8J Quantity: 1
+ For more information about the disposal order process, see Remove inventory from a fulfilment centre .
+ To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
+ The Fulfilment by Amazon Team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Disposal order created for unsellable FBA inventory</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated Removals of Unfulfillable Inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Hello,
+You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
+ Why is this happening?
+This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
+ Removal order ID:
+- AJ3wMIfu1v
+ Unsellable Products:
+- FNSKU: X002A05YW5 Quantity: 1
+ For more information about the disposal order process, see Remove inventory from a fulfilment centre .
+ To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
+ The Fulfilment by Amazon Team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Reminder: Please share your feedback on MCF</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Reminder: Please share your feedback on MCF
+Dear Weihai US,
+As a valued Multi-Channel Fulfillment (MCF) managed customer, we are interested in learning about your program feedback including new features that may benefit your business. This may help us understand how we can better meet your business needs and continue to improve the customer experience. Please complete this survey no later than March 19.
+(button)  Click here to complete survey  https://amazonexteu.qualtrics.com/jfe/form/SV_et9BAqtoDGCsCB8?Q_CHL=gl&amp;amp;Q_DL=EMD_Z45pcIhoS9Jgg2Y_et9BAqtoDGCsCB8_CGC_gVqjuURBQB4eTq0&amp;amp;_g_=g
+This submission form is unique to your Seller account and can only be submitted once.
+DISCLAIMER: Please do not include any Personally Identifiable Information within this survey such as physical addresses, phone numbers, merchant tokens, email addresses, account data, etc.
+Thank you,
+Your Multi-Channel Fulfillment Team
+This survey is hosted by an external party Qualtrics.com, so the link above does not lead to our website. Your responses are subject to Amazon's Privacy Notice. If you have any concerns about the authenticity of this e-mail or to find out more about Amazon's survey program, please vi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Tu pago está en camino</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
+El 03/19/26 15:38 WET, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 74,59.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un éxit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.com Inventory - Action Required</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Dear Weihai US,
+We have recently restricted listings for the product(s) listed below on Amazon.com.
+Please initiate a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing. If this inventory is not removed within 30 days of this notification (by 04/12/2026), we may dispose of it in accordance with FBA policies.
+Thank you for your attention to this matter.
+Regards,
+Product Safety Team
+Amazon.com
+www.amazon.com
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
+Affected Product(s):
+B0FCDRNTT8
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
+SPC-USAmazon-1917550476493542</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
+ For step-by-step instru</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
+Dear there,
+Thank you for being a valued member of the Amazon Multichannel Fulfillment (MCF) and Buy with Prime community. We are reaching again out to make sure you have seen that starting in April 2026, MCF and Buy with Prime will introduce two updates to how orders are packaged and shipped in the United States:
+Packing slips will no longer be included by default.
+Items already certified for the Ships in Product Packaging (SIPP) program on Amazon.com will ship without an Amazon overbox by default.
+In addition, eligible MCF and Buy with Prime SIPP shipments will receive a discount. See the SIPP for MCF help content for details.
+https://www2.amazonsupplychain.com/e/949422/ence-external-GVCFXDFYNCTFLTTQ/61b9cx/1372255659/h/xX050fPuJyuSx_HuFPheaHfGRXD19yafaiWekQ5-4Gg
+Packing slips will no longer be included by default.
+Items already certified for the Ships in Product Packaging (SIPP) program on Amazon.com will ship without an Amazon overbox by default.
+In addition, eligible MCF and Buy with Prime SIPP shipments will receive a discount. See the SIPP for MCF help content for details.
+These updates support Amazon’s co</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Seller News: March 2026</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services
+ 96
+ Updates to Seller Central workspaces, Upload Images, Product Opportunity explorer, and more.
+ Our Seller Newsletter provides the most important policy, tool, and program updates from the past month. Stay informed about selling on Amazon.
+ Introducing a new, AI-powered workspace
+ You now have access to a dynamic canvas experience in Seller Central, where you can visualize data and key insights, explore scenarios, and take critical actions to grow your business. This integrated, AI-native workspace combines chat and visual elements to provide highly personalized and actionable insights. Read more .
+ Upload Images now provides faster uploads and more flexibility
+ We’ve enhanced the image upload process in Upload Images to make managing images for your product catalog faster and more flexible. Read more .
+ Remove meltable FBA inventory by April 20
+ To meet product quality standards, we won’t accept meltable inventory at our fulfillment centers between April 20, 2026, and September 28, 2026. Meltable inventory remaining in our fulfillment centers after April 20, may be marked unfillable and disposed of for a fee, starting May 1, 2026. Read more .
+ Save and track pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Act today &amp; improve Sales on Excess Inventory</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Optional preview text
+ Hello,
+We noticed you have a number of ASIN(s) that have excess levels of inventory. We are reaching out to inform you about multiple options to improve your Unit Sales on your aged and/or excess inventory in Amazon Fulfillment Centers. Our goal is to help you increase the sales on this excess inventory:
+X004QEYPRL, X004QFJQLF, X004MMFUYT, X004QEVV05, X004K6ILMZ
+We encourage you to take Amazon recommended actions such as Create Outlet deals, Sponsor Products Ad, to improve sell through of this excess inventory and potentially reduce your chances of incurring aged inventory fee.
+ Outlet deals
+ Amazon Outlet is a great place for customers to shop for overstock deals, which offers a selection of items, such as electronics, toys, beauty, and kitchen.
+ Create Outlet Deal Today!
+ Sponsored Product Ads
+ Sponsored Products is a cost-per-click advertising solution that provides advertisers with a foundation of controls and visibility to help get their individual products discovered, and help generate sales from traffic sources in the Amazon store and on select premium apps and websites.
+ Create Sponsored Products Ad Today!</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Seller News: March 2026</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services
+ 96
+ Stay informed about selling on Amazon.
+ Our Seller Newsletter provides the most important policy, tool and programme updates from the past month.
+ Introducing a new, AI-powered workspace
+ You now have access to a dynamic canvas experience in Seller Central, where you can visualise data and key insights, explore scenarios and take critical actions to grow your business. This integrated, AI-native workspace combines chat and visual elements to provide highly personalised and actionable insights. Read more .
+ Upload Images now provides faster uploads and more flexibility
+ We’ve enhanced the image upload process in Upload Images to make managing images for your product catalogue faster and more flexible. Read more .
+ Save and track product research with Product Opportunity Explorer
+ Product Opportunity Explorer now includes a feature that helps you save and organise your research. You can identify profitable opportunities with low competition and save those promising product niches and ASINs with a single click. Read more .
+ Account health tips for multiple selling accounts
+ Our multiple-accounts policy allows you to operate one account per region unless you have a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>A Amazon enviou os itens vendidos</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
+ Olá,
+ Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon para clientes. Veja os detalhes abaixo para até 20 dos pedidos mais recentes.
+ Para acompanhar o status desses pedidos e de todos os seus pedidos, acesse a página Gerenciar pedidos no Seller Central.
+ Os seguintes itens do pedido completo foram enviados por Amazon.com.br para:
+ Número do pedido: 702-3877609-2537851
+ Quantidade
+ Item do pedido
+ Enviado por
+ 1
+ Roaxkois Roda de cerâmica para crianças - Kit completo de pintura de artes e artesanato DIY com argila seca ao ar, tintas, ferramentas, avental e ad
+ SKYPOSTAL
+ Rastreamento: SKAMZUS0075085120
+Observe que a entrega durante o fim de semana não está disponível para nossas opções de Entrega em dois dias ou Entrega no dia seguinte. Os pacotes enviados de um centro de distribuição no sábado ou domingo só chegarão ao remetente na segunda-feira de manhã.
+Para obter ajuda com seu pedido, você pode encontrar links para enviar um e-mail ou ligar para o Suporte técnico de conta no link Fale conosco no Seller Central.
+Obrigado.
+Equipe do programa FBA - Logística da Amazon
+ Este e-m</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Pagamento elaborato con successo</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulazioni. Il pagamento è stato elaborato con successo e ti sarà accreditato a breve.
+ Tentativo di pagamento
+Congratulazioni Weihai EU! Il pagamento è stato elaborato con successo e ti sarà accreditato nel giro di da tre a cinque giorni.
+In data 03/15/26 14:54 CET, abbiamo avviato un trasferimento sul tuo metodo di pagamento (conto bancario che termina con 229) dell’importo di €
+ 200,42.
+ Se l’importo è inferiore a quanto atteso, tieni in considerazione le seguenti domande:
+ Hai un saldo non disponibile? Amazon potrebbe trattenere una certa somma per coprire i costi di eventuali resi, reclami o contestazioni di una transazione (chargeback) da parte degli acquirenti. In questo caso, il saldo finale nel tuo report sui pagamenti mostrerà il saldo non disponibile corrispondente alla cifra trattenuta.
+ Le tue vendite coprono tutte le commissioni e i resi per questo ciclo di fatturazione? L’importo del pagamento rispecchia le attività di vendita, le commissioni di vendita e le tariffe per promozioni o servizi. Ti consigliamo di rivedere il report sui pagamenti nella scheda Report di Seller Central per comprendere le diverse spese che p</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Hola, Weihai EU:
+ Para cumplir nuestros requisitos de registro del impuesto sobre el valor añadido (IVA) europeo, necesitamos que nos proporciones más información.
+ ¿A qué se debe esto?
+ De acuerdo con nuestros requisitos de registro a efectos fiscales en Europa, tienes que proporcionarnos un número de identificación fiscal válido de todos los países en los que consideremos que tienes obligación de registrarte a efectos fiscales o confirmar el estado de registro en la Ventanilla Única del IVA (OSS) en tu país de origen.
+ Hemos detectado que tu cuenta tiene que cumplir una serie de requisitos para el registro a efectos fiscales en la Unión Europea, el Reino Unido, Noruega y Suiza, donde tienes la obligación de registrarte a efectos fiscales. En concreto, es posible que tengas que tomar medidas para lo siguiente:
+ Polonia
+ Para más información, consulta Información sobre el impuesto sobre el valor añadido (IVA) europeo .
+ ¿Cómo evito la desactivación de mi cuenta?
+ Para evitar la desactivación de la cuenta, consulta la sección "Acciones prioritarias" de la página Estado de la cuenta en los próximos 45 días. Desde ahí podrás hacer lo siguiente:
+- Revisar la información que tienes </t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Dzień dobry Weihai EU,
+ potrzebujemy od Ciebie dodatkowych informacji, które pozwolą Ci spełnić europejskie wymagania Amazon dotyczące rejestracji jako podatnik VAT.
+ Dlaczego tak się stało?
+ Zgodnie z europejskimi wymaganiami Amazon dotyczącymi rejestracji jako podatnik VAT musisz podać nam ważny numer VAT dla wszystkich krajów, w których według nas podlegasz obowiązkowi rejestracji jako podatnik VAT, lub potwierdzenie statusu rejestracji w procedurze unijnej w Twoim kraju macierzystym.
+ Ustaliliśmy, że w przypadku Twojego konta w Unii Europejskiej, Zjednoczonym Królestwie, Norwegii i Szwajcarii, gdzie masz zobowiązania z tytułu VAT, istnieją wymogi w zakresie rejestracji jako podatnik VAT. Podjęcie działań może być w szczególności wymagane w następujących przypadkach:
+ Polska
+ Więcej informacji znajdziesz na stronie Informacje dotyczące podatku VAT w Europie .
+ Jak mogę zapobiec dezaktywacji konta?
+ Aby uniknąć dezaktywacji konta, w ciągu najbliższych 45 dni odwiedź sekcję „Działania priorytetowe” na stronie Kondycja konta . W sekcji tej można:
+- zweryfikować istniejące informacje dotyczące wymienionych krajów
+- przesłać informacje o VAT za pośrednictwem portali „Informacje o</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
+ la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Gentile Weihai EU,
+ Ai fini della conformità ai requisiti di registrazione IVA in Europa di Amazon, ti chiediamo di fornirci ulteriori informazioni.
+ Ciò a cosa è dovuto?
+ In base ai requisiti di registrazione IVA in Europa di Amazon, sei tenuto a fornirci un numero di partita IVA valido per tutti i paesi in cui riteniamo che tu abbia l'obbligo di effettuare tale registrazione o una conferma dello stato Union One-Stop Shop (OSS) relativo al tuo paese di registrazione.
+ Vi sono dei requisiti per la registrazione ai fini IVA che il tuo account deve soddisfare nei paesi in cui sei soggetto a obblighi in materia di IVA (stati dell'Unione europea, Regno Unito, Norvegia e Svizzera). Nello specifico, potrebbe essere necessario un intervento da parte tua per quanto segue:
+ Polonia
+ Per maggiori informazioni, consulta la pagina di aiuto Informazioni sull'IVA in Europa .
+ Come faccio a evitare la disattivazione dell'account?
+ Per evitare la disattivazione dell'account, visita entro i prossimi 45 giorni la sezione relativa alle azioni prioritarie della pagina Stato dell'account . Da qui, potrai effettuare le seguenti operazioni:
+- Verificare le informazioni esistenti per i paesi in elenco</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96
+Amazon UAE
+ Amazon Announcement
+ Hello,
+ We previously communicated that Fulfillment by Amazon (FBA) removal fees would be introduced in the UAE and Saudi Arabia on March 30, 2026.
+Due to the developing situation in the Middle East, we will not apply FBA removal fees in UAE and Saudi Arabia until further notice . No fees will apply for FBA removal orders initiated by you or Amazon.
+We will notify you of any future change to this policy in advance.
+The Amazon Services team
+- .
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+ SPC-EUAmazon-1794404611296645</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Disposal order created for unsellable FBA inventory</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated Removals of Unfulfillable Inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Hello,
+You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
+ Why is this happening?
+This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
+ Removal order ID:
+- rJ8tXXz1/k
+ Unsellable Products:
+- FNSKU: X002A05YW5 Quantity: 1
+ For more information about the disposal order process, see Remove inventory from a fulfilment centre .
+ To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
+ The Fulfilment by Amazon Team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferen</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>[Action Required] Provide additional information within 45 days to
+ avoid account deactivation under European VAT registration requirements</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai EU,
+ We need you to provide additional information in order to comply with Amazon’s European Value Added Tax (VAT) registration requirements.
+ Why is this happening?
+ According to Amazon’s European VAT registration requirements you must provide us with a valid VAT Registration Number (‘VRN’) for all the countries in which we believe you have a VAT registration obligation or confirmation of the Union One-Stop Shop (OSS) status for your home country.
+ We identified VAT registration requirements for your account in the European Union, the United Kingdom, Norway, and Switzerland in which you have VAT obligation. Specifically, action may be required for the following:
+ Poland
+ To learn more, go to the European Value Added Tax Information Help page.
+ How do I avoid account deactivation?
+ To avoid account deactivation, within the next 45 days visit the Priority Actions section on your Account Health page . From there, you will be able to:
+- Verify your existing information for listed countries
+- Submit VAT information through Business Information and Tax Setting portals
+- Submit required documentation for extension or exemption requests
+ What happens if I don’t provide th</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>[Action required] Provide additional information within 45 days to
+ avoid account deactivation under European VAT registration requirements</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai EU,
+ We need you to provide additional information in order to comply with Amazon’s European Value Added Tax (VAT) registration requirements.
+ Why is this happening?
+ According to Amazon’s European VAT registration requirements, you must provide us with a valid VAT registration number (“VRN”) for all the countries in which we believe you have a VAT registration obligation, or confirmation of the Union One-Stop Shop (OSS) status for your home country.
+ We identified VAT registration requirements for your account in the European Union, the United Kingdom, Norway and Switzerland in which you have Value Added Tax (VAT) obligation. Specifically, action may be required for the following:
+ Poland
+ To learn more, go to the European Value Added Tax information help page.
+ How do I avoid account deactivation?
+ To avoid account deactivation, within the next 45 days visit the Priority actions section on your Account Health page . From there, you will be able to:
+- Verify your existing information for listed countries
+- Submit Value Added Tax (VAT) information through business information and tax setting portals
+- Submit required documentation for extension or exemption request</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
+ votre compte vendeur Amazon</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon Services.
+ We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
+ Note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. If that is the case, we will continue to charge your card as often as every 24 hours until the remaining balance in your Amazon seller account is paid in full.
+ You can also use the Make a Payment feature to repay the balance you owe. For details, go to seller Help, and search for “Make a Payment.”
+ You can view your payment activity at any time by logging in to your seller account and going to your Payments Report.
+ Thank you for selling on Amazon.ca.
+ Amazon Services
+ *****
+ Bonjour d’Amazon Services,
+ Nous avons débité votre carte bancaire (Visa) pour CDN$ 44.03 pour le règlement du solde de votre compte vendeur.
+ Le montant débité sur votre carte bancaire peut être inférieur au montant total impayé si vous disposez d'une limite de crédit imposée par votre banque. Nous continuerons d'essayer de débiter votre carte bancaire toutes les 24 heures jusqu'à ce que le solde restant de votre compte soit e</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral-europe.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-9215101-5718342
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+------------------------------------------------------------------------------
+Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
+and EU wide.
+------------------------------------------------------------------------------
+Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-EUAmazon-1495337446934234</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Please share your feedback on MCF</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Please share your feedback on MCF
+Dear Weihai US,
+As a valued Multi-Channel Fulfillment (MCF) managed customer, we are interested in learning about your program feedback including new features that may benefit your business. This may help us understand how we can better meet your business needs and continue to improve the customer experience. Please complete this survey no later than March 19.
+(button)  Click here to complete survey  https://amazonexteu.qualtrics.com/jfe/form/SV_et9BAqtoDGCsCB8?Q_CHL=gl&amp;amp;Q_DL=EMD_Z45pcIhoS9Jgg2Y_et9BAqtoDGCsCB8_CGC_gVqjuURBQB4eTq0&amp;amp;_g_=g
+This submission form is unique to your Seller account and can only be submitted once.
+DISCLAIMER: Please do not include any Personally Identifiable Information within this survey such as physical addresses, phone numbers, merchant tokens, email addresses, account data, etc.
+Thank you,
+Your Multi-Channel Fulfillment Team
+This survey is hosted by an external party Qualtrics.com, so the link above does not lead to our website. Your responses are subject to Amazon's Privacy Notice. If you have any concerns about the authenticity of this e-mail or to find out more about Amazon's survey program, please visit the Am</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (FVSl6sGweZ)</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral-europe.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-7813814-2599064
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+------------------------------------------------------------------------------
+Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
+and EU wide.
+------------------------------------------------------------------------------
+Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-EUAmazon-1108309350654781</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 17:16:27 +0000</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+The following automated unfulfillable FBA removal orders have been created based on your automated settings.
+ Removal order ID UvRxALtvwM
+ You can view the removals on Removal Order Details in your seller account by using the Search tool.
+The next removal order will be created as scheduled on March 20, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
+To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
+ Thank you.
+The Fulfillment by Amazon team
+Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+ SPC-USAmazon-404622472692539</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 04:02:47 +0000</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (uih6sNeVfd)</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral-europe.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-4201829-9256139
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+------------------------------------------------------------------------------
+Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
+and EU wide.
+------------------------------------------------------------------------------
+Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-EUAmazon-844426561416317</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 2 Mar 2026 20:32:33 +0000</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (DjHMcVqBnq)</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral-europe.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-5905698-4511047
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+------------------------------------------------------------------------------
+Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
+and EU wide.
+------------------------------------------------------------------------------
+Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-EUAmazon-1600890559216565</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 26 Feb 2026 15:54:28 +0000</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
+ votre compte vendeur Amazon</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon Services.
+ We have charged your credit card (Visa) for CDN$ 29.08 in an attempt to settle your Amazon.ca seller account balance.
+ Note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. If that is the case, we will continue to charge your card as often as every 24 hours until the remaining balance in your Amazon seller account is paid in full.
+ You can also use the Make a Payment feature to repay the balance you owe. For details, go to seller Help, and search for “Make a Payment.”
+ You can view your payment activity at any time by logging in to your seller account and going to your Payments Report.
+ Thank you for selling on Amazon.ca.
+ Amazon Services
+ *****
+ Bonjour d’Amazon Services,
+ Nous avons débité votre carte bancaire (Visa) pour CDN$ 29.08 pour le règlement du solde de votre compte vendeur.
+ Le montant débité sur votre carte bancaire peut être inférieur au montant total impayé si vous disposez d'une limite de crédit imposée par votre banque. Nous continuerons d'essayer de débiter votre carte bancaire toutes les 24 heures jusqu'à ce que le solde restant de votre compte soit e</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 26 Feb 2026 06:14:30 +0000</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA removal request is complete (X8HTY1kPjb)</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed and shipped your removal
+request (X8HTY1kPjb) to the address you specified before.
+Return Summary:
+Quantity Requested: 1
+Quantity Successfully Shipped: 1
+Quantity Cancelled: 0
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral.amazon.com/
+For a complete list of inventory being shipped, go to:
+https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-0304844-4961146
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+--------------------------------------------------------------------------
+Fulfillment by Amazon, professional packing, shipping and servicing of
+online orders.
+--------------------------------------------------------------------------
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-USAmazon-703689634178458</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 21 Feb 2026 17:52:28 +0000</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+The following automated unfulfillable FBA removal orders have been created based on your automated settings.
+ Removal order ID X8HTY1kPjb
+ You can view the removals on Removal Order Details in your seller account by using the Search tool.
+The next removal order will be created as scheduled on March 5, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
+To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
+ Thank you.
+The Fulfillment by Amazon team
+Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+ SPC-USAmazon-1231455213477503</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 19 Feb 2026 21:45:54 +0000</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA removal request is complete (SOu11lTFx5)</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed and shipped your removal
+request (SOu11lTFx5) to the address you specified before.
+Return Summary:
+Quantity Requested: 2
+Quantity Successfully Shipped: 2
+Quantity Cancelled: 0
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral.amazon.com/
+For a complete list of inventory being shipped, go to:
+https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-4303247-5655239
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+--------------------------------------------------------------------------
+Fulfillment by Amazon, professional packing, shipping and servicing of
+online orders.
+--------------------------------------------------------------------------
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-USAmazon-738874004554169</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 19 Feb 2026 03:59:48 +0000</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 18 Feb 2026 09:45:35 +0000</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfillment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfillment center. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.com/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.com/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+- T</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Balance Paid on Your Selling on Amazon payment account</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+ We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
+ Please note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. In this case, we may continue to attempt charging your card until the remaining balance in your Amazon Selling on Amazon payment account is paid in full.
+ You can also use the Make a Payment feature to repay the balance you owe. For details, refer “Making a Payment” in Seller Central Help.
+ To view your payment activity anytime, please log in to your account and refer the Payments Report page.
+ Thank you for selling on Amazon.
+ Amazon Payments UK Limited
+Amazon Payments UK Limited, a private company limited by shares, is a company registered in England and Wales (registration number 11049457; VAT number: GB295 7604 60) with its registered office at 1 Principal Place, Worship St, London, EC2A 2FA, United Kingdom. Amazon Payments UK Limited is authorised by the UK Financial Conduct Authority under the Payment Services Regulations 2017 (reference number 799814) for the provision of payment services.
+ Was this e-mail helpful?
+ SPC-EUAma</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Nous avons ajusté votre solde négatif 4.08 € dû sur votre compte vendeur Amazon.be le mars 11, 2026 à partir de fonds disponibles sur votre compte Amazon.de. Vous pouvez consulter le solde de votre compte à tout moment en vous connectant à votre compte et en accédant au tableau de bord des paiements .
+Pour plus d'informations, consultez la rubrique Ajustement du solde négatif sur l'ensemble de vos comptes .
+Cordialement,
+Amazon Payments Europe
+ Signaler un problème avec cet e-mail
+ Pour toute question, rendez-vous sur : Seller Central
+ Pour modifier vos préférences d’e-mail, accédez à la page : Préférences de notification
+ Copyright 2026 Amazon, Inc. ou ses filiales. Tous droits réservés.
+ Amazon Payments Europe
+38 Avenue John F. Kennedy
+L-1855 Luxembourg,
+Enregistré au Luxembourg n° B-101818,
+Capital social : 165 833 EUR,
+Numéro de licence commerciale : 134248,
+Luxembourg Nº de TVA LU 20260743
+ Cet e-mail provient d’une adresse e-mail qui n’autorise pas les réponses.
+ SPC-EUAmazon-774057817782756</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 15:16:36 +0000</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Nieuregulowane saldo na koncie Amazon</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Witamy!
+ Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 30.46. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
+ Jeśli ta karta ma limit kredytowy, możemy ją obciążać do momentu pełnej spłaty nieuregulowanego salda.
+ Aby uzyskać więcej informacji, wyszukaj Dokonaj płatności w Pomocy Seller Central.
+ Aby dowiedzieć się więcej na temat raportów płatności i Twoich działań, wyszukaj Wyświetl moje raporty o płatnościach w Pomocy Seller Central.
+ Z poważaniem,
+ Amazon Payments Europe SCA (société en commandite par actions) to spółka komandytowo-akcyjna zarejestrowana w Luksemburgu, numer rejestracyjny (RCS Luxembourg) B 153 265, z siedzibą pod adresem 38 avenue J.F. Kennedy, L-1855 Luxembourg. Numer VAT: LU 24448288. Amazon Payments Europe SCA posiada upoważnienie Komisji Nadzoru Sektora Finansowego w Luksemburgu do emisji pieniądza elektronicznego (numer licencji 36/10)
+ Czy ten e-mail był pomocny?
+ SPC-EUAmazon-1037940607738415</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 8 Mar 2026 14:57:34 +0000</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Negatieve saldoaanpassing voor al je accounts</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ We hebben je negatieve saldo van €11.99 dat verschuldigd was via je Amazon.nl verkopersaccount op maart 8, 2026, aangepast met geld dat beschikbaar was in je Amazon.it account. Je kunt je accountsaldo op elk gewenst moment bekijken door in te loggen op je account en naar het Betalingsdashboard te gaan.
+Ga voor meer informatie naar Negatieve saldoaanpassing voor al je accounts .
+Met vriendelijke groet,
+Amazon Payments Europe
+ Rapporteer een probleem met deze e-mail
+ Als je vragen hebt, ga dan naar: Seller Central
+ Om je e-mailvoorkeuren te wijzigen, ga je naar: Voorkeuren voor meldingen
+ Auteursrecht (copyright) 2026 Amazon, Inc. of haar dochterondernemingen. Alle rechten voorbehouden.
+ Amazon Payments Europe S.C.A. (société en commandite par actions), een commanditaire vennootschap op aandelen, is een bedrijf dat is geregistreerd in Luxemburg onder registratienummer (RCS Luxembourg) B 153 265, met het hoofdkantoor op 38 Avenue J.F. Kennedy, L-1855 Luxemburg. Btw-nummer LU 24448288.
+ Amazon Payments Europe S.C.A. is geautoriseerd door de Commission de Surveillance du Secteur Financier in Luxemburg en staat onder toezicht van de Central B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 8 Mar 2026 13:38:27 +0000</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai US! Your payment is on the way and will arrive within three to five days.
+On 03/08/26 13:38 PDT, we initiated a transfer to your payment method (bank account ending in 003) in the amount of $
+ 108.10.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+ Amazon sellers and Amazon Pay merchants can si</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 5 Mar 2026 15:38:46 +0000</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Tu pago está en camino</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
+El 03/05/26 15:38 WET, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 93,03.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un éxit</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 3 Mar 2026 16:06:24 +0000</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Rettifica del saldo negativo nei tuoi account</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Abbiamo rettificato il tuo saldo negativo di 235.86 € dovuto dal tuo account venditore Amazon.it in data marzo 3, 2026, utilizzando i fondi disponibili nei tuoi account Amazon.fr, Amazon.es. Puoi visualizzare il saldo del tuo account in qualsiasi momento accedendo al tuo account e quindi alla dashboard dei pagamenti .
+Per maggiori informazioni, vai a Rettifica del saldo negativo nei tuoi account .
+Distinti saluti,
+Amazon Payments Europe
+ Segnala un problema con questa e-mail
+ Per qualsiasi domanda consulta: Seller Central
+ Per modificare le preferenze sulle e-mail consulta: Preferenze sulle notifiche
+ Copyright 2026 Amazon, Inc. o società affiliate. Tutti i diritti riservati.
+ Amazon Payments Europe
+ 38 avenue John F. Kennedy,
+ L-1855 Lussemburgo,
+ Numero di registrazione in Lussemburgo: B-101818,
+ Capitale Sociale 165.833 EUR,
+ Numero di licenza di attività commerciale: 134248,
+ Partita IVA n. LU 20260743.
+ Questa e-mail è stata inviata da un indirizzo e-mail non monitorato.
+ SPC-EUAmazon-387029723704225</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 3 Mar 2026 14:48:41 +0000</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
+On 03/03/26 14:48 SAST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of SAR
+ 2181.23.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+Help us improve your payment experience on </t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 26 Feb 2026 14:12:31 +0000</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
+On 02/26/26 14:12 GMT, we initiated a transfer to your payment method (bank account ending in 191) in the amount of £
+ 203.26.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To find out more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+Help us improve your payment experience on Ama</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 24 Feb 2026 14:54:33 +0000</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Twoja płatność jest już w drodze</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>96
+Ten tytuł będzie wyświetlany na urządzeniach mobilnych
+ Gratulujemy! Twoja płatność jest już w drodze, a środki powinny wkrótce do Ciebie dotrzeć.
+ Próba wypłaty środków
+Gratulacje, Weihai EU! Twoja płatność jest już w drodze, a środki powinny do Ciebie dotrzeć w terminie od trzech do pięciu dni.
+Dnia 02/24/26 14:54 CET zainicjowaliśmy przelew na kwotę PLN
+ 88.25 na konto powiązane z Twoją metodą płatności (rachunek bankowy o ostatnich cyfrach 229).
+ Jeśli kwota jest mniejsza niż oczekiwana, oto kilka kwestii do wzięcia pod uwagę:
+ Czy Twoje saldo jest niedostępne? Amazon może zatrzymać środki na pokrycie ewentualnych kosztów zwrotów towarów, roszczeń i obciążeń zwrotnych od kupujących. W takim przypadku saldo zamknięcia w raporcie płatności pokaże niedostępne saldo na zarezerwowaną w tym celu kwotę.
+ Czy Twoja sprzedaż wystarczyła na pokrycie wszystkich opłat i zwrotów w tym okresie rozliczeniowym? Kwota płatności uwzględnia koszt działań sprzedażowych, opłaty za sprzedaż oraz opłaty za promocje i usługi. Aby lepiej zrozumieć wysokość salda zamknięcia, warto przeanalizować raport płatności, który znajdziesz w Seller Central w karcie „Raporty”.
+Więcej o raportach płatności w Sel</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 22 Feb 2026 13:38:32 +0000</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai US! Your payment is on the way and will arrive within three to five days.
+On 02/22/26 13:38 PST, we initiated a transfer to your payment method (bank account ending in 003) in the amount of $
+ 216.13.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+ Amazon sellers and Amazon Pay merchants can si</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 22 Feb 2026 13:37:02 +0000</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
+On 02/22/26 13:36 GMT, we initiated a transfer to your payment method (bank account ending in 191) in the amount of £
+ 352.86.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To find out more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+Help us improve your payment experience on Ama</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 19 Feb 2026 15:49:30 +0000</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Payments Europa &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Ajuste de saldo negativo en tus cuentas de Vender en Amazon</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Hemos ajustado tu saldo negativo de €3.55 que se adeudaba de tu cuenta de vendedor Amazon.es en febrero 19, 2026, con fondos que estaban disponibles en tu cuenta Amazon.fr. Puedes ver el saldo de tu cuenta en cualquier momento accediendo a tu cuenta y navegando hasta el panel de control Pagos .
+Para más información, consulta la sección Ajuste de saldo negativo en tus cuentas .
+Atentamente,
+Amazon Payments Europa
+ Informar de un problema con este correo electrónico
+ Si tienes alguna pregunta, consulta: Seller Central
+ Para modificar tus preferencias de correo electrónico, consulta: Preferencias de notificación
+ Copyright 2026 Amazon, Inc. o sus filiales. Todos los derechos reservados.
+ Amazon Payments Europe
+ 38 avenue John F. Kennedy,
+ L-1855 Luxemburgo,
+ Número de Registro en Luxemburgo: No. B-101818,
+ Capital Social 165.833 EUR,
+ Número de licencia de actividad: 134248,
+ Nº de Registro IVA en Luxemburgo: LU 20260743.
+ Este mensaje se envía desde una dirección de correo electrónico sin supervisión.
+ SPC-EUAmazon-1776812415580202</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 19 Feb 2026 12:00:21 +0000</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai US! Your payment is on the way and will arrive within three to five days.
+On 02/19/26 12:00 PST, we initiated a transfer to your payment method (bank account ending in 003) in the amount of $
+ 219.30.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+ Amazon sellers and Amazon Pay merchants can si</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>尊敬的卖家：
+我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
+① 提交TRF（务必在确认好合作的TIC或进行第二步之前完成，并确保TRF ID成功生成）
+• 登录卖家平台，进入【绩效 &gt; 账户状况 &gt; 食品和商品安全问题】，找到需处理ASIN
+• 点击右侧【提交】，选定TIC服务提供商后点击【继续】提交TRF，完成可在页面查看TRF ID。
+② 向TIC服务提供商支付费用；
+③ 向TIC服务提供商寄送产品样品或提交您已有的外部检测报告或合规文件。
+④ 确保TIC服务商将TRF状态更新为【正在验证】
+如何查看TRF状态：在绩效 &gt; 账户状况 &gt; 食品和商品安全问题找到ASIN，点击右方“提交，查看或更新”&gt;“验证您的商品”
+⚠️请注意：
+① 同一ASIN可能只在部分欧洲站点被触发通知，若您计划在欧洲（英国及欧盟）继续销售，只需为每个ASIN任选一个站点完成合规，测试结果将同步至全欧站点。
+② 由于数据可能存在延迟，请务必以卖家平台【绩效 &gt; 账户状况 &gt; 食品和商品安全问题】页面显示的最新状态为准。
+③ 如果您认为您的产品不属于【儿童玩具】产品，请选择【申诉请求】选项，提供您认为产品被错误识别的原因进行申诉。
+感谢您的支持，祝您合规大卖
+如有疑问，请扫码加入亚马逊卖家合规群：
+https://m.media-amazon.com/images/G/01/CN_Compliance_Team/mass_wecom_yt.jpg
+Amazon Global Selling Seller Compliance Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>尊敬的卖家：
+我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
+① 提交TRF（务必在确认好合作的TIC或进行第二步之前完成，并确保TRF ID成功生成）
+• 登录卖家平台，进入【绩效 &gt; 账户状况 &gt; 食品和商品安全问题】，找到需处理ASIN
+• 点击右侧【提交】，选定TIC服务提供商后点击【继续】提交TRF，完成可在页面查看TRF ID。
+② 向TIC服务提供商支付费用；
+③ 向TIC服务提供商寄送产品样品或提交您已有的外部检测报告或合规文件。
+④ 确保TIC服务商将TRF状态更新为【正在验证】
+如何查看TRF状态：在绩效 &gt; 账户状况 &gt; 食品和商品安全问题找到ASIN，点击右方“提交，查看或更新”&gt;“验证您的商品”
+⚠️请注意：
+①如果您认为您的产品不属于【儿童玩具】产品，请选择【申诉请求】选项，提供您认为产品被错误识别的原因进行申诉。
+②由于数据可能存在延迟，请务必以卖家平台【绩效 &gt; 账户状况 &gt; 食品和商品安全问题】页面显示的最新状态为准。
+感谢您的支持，祝您合规大卖!
+如有疑问，请扫码加入亚马逊卖家合规群：
+https://m.media-amazon.com/images/G/01/CN_Compliance_Team/mass_wecom_sw.jpg
+To contact us again about this issue, please use the Contact Us form in Seller Central using the following link:
+https://sellercentral.amazon.com/cu/case-dashboard/view-case?caseID=18425733131
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 20:15:20 +0000</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to avoid listing deactivation</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai EU,
+ Some of your listings are at risk of deactivation due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
+ For step-by-step instructions, see our Submit compliance documents or appeal a documentation request help page.
+ To avoid further impact to your account, close or delete any non-compliant listings that you do</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 5 Mar 2026 21:09:14 +0000</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to avoid listing deactivation</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai EU,
+ Some of your listings are at risk of deactivation due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listing?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents.
+-
+ If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
+ For step-by-step instructions, see our Submit compliance documents or appeal a documentation request help page.
+ To avoid further impact on your account, close or delete any non-compliant listings that you</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 5 Mar 2026 20:28:43 +0000</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Address compliance requirements for your listings</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>96
+Action required: Important information about your product listings
+ We are contacting you because you have listed products that require you to submit compliance documents.
+ Product listings are missing required compliance documents
+ Hello,
+ We are contacting you because you have listed products that require you to submit compliance documents. Click on Review Compliance Requirements below to see the list of affected products and submit the required compliance documents. If you do not submit the documents by the due date indicated for each product in this link, we may remove the affected listings.
+ Review Compliance Requirements
+ The table below contains a sample of your affected listings. Click on Review Compliance Requirements to see all of your affected listings.
+ SKU ASIN Listing Status WHEUSGMH81901 B0DD7R3PPG At risk of removal
+ Why is this happening?
+This requirement helps to ensure that products are compliant with local laws and safe for customers.
+ How do I continue to sell the affected products?
+Click on Review Compliance Requirements to find out more information about the documents you need to provide for each product.
+ Was there an error?
+If you believe that you do not</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 5 Mar 2026 20:28:31 +0000</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Address compliance requirements for your listings</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>96
+Action required: Important information about your product listings
+ We are contacting you because you have listed products that require you to submit compliance documents.
+ Product listings are missing required compliance documents
+ Hello,
+ We are contacting you because you have listed products that require you to submit compliance documents. Click Review Compliance Requirements below to see the list of affected products and submit the required compliance documents. If you do not submit the documents by the due date indicated for each product in this link, we may remove the affected listings.
+ Review Compliance Requirements
+ The table below contains a sample of your affected listings. Click Review Compliance Requirements to see all of your affected listings.
+ SKU ASIN Listing Status WHEUSGMH81901 B0DD7R3PPG At risk of removal
+ Why is this happening?
+This requirement helps ensure that products are compliant with local laws and safe for customers.
+ How do I continue to sell the affected products?
+Click Review Compliance Requirements to find out more information about the documents you need to provide for each product.
+ Was there an error?
+If you believe that you do not need to sub</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 5 Mar 2026 20:28:14 +0000</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Vereisten voor naleving van je productvermeldingen aanpakken</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>96
+Actie vereist: Belangrijke informatie over je productvermeldingen
+ We nemen contact met je op omdat je producten hebt vermeld waarvoor je nalevingsdocumenten moet indienen.
+ Productvermeldingen ontbreken vereiste nalevingsdocumenten
+ Hallo,
+ We nemen contact met je op omdat je producten hebt vermeld waarvoor je nalevingsdocumenten moet indienen. Klik hieronder op Nalevingsvereisten bekijken om de lijst met betrokken producten te bekijken en de vereiste nalevingsdocumenten in te dienen. Als de documenten nog niet zijn ingediend op de vervaldatum die voor elk product in deze link is aangegeven, kunnen we de betreffende productvermeldingen verwijderen.
+ Nalevingsvereisten bekijken
+ In de onderstaande tabel zie je een voorbeeld van je betrokken productvermeldingen. Klik op Nalevingsvereisten bekijken om al je betrokken productvermeldingen weer te geven.
+ SKU ASIN Status van productvermelding WHEUSGMH81901 B0DD7R3PPG Risico van verwijdering
+ Waarom gebeurt dit?
+Met deze vereiste zorgen we ervoor dat producten voldoen aan de lokale wetgeving en veilig zijn voor klanten.
+ Hoe kan ik de betrokken producten blijven verkopen?
+Klik op Nalevingsvereisten bekijken voor meer informatie over d</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Hantera efterlevnadskrav för dina produktposter</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>96
+Åtgärd krävs: Viktig information angående dina produktposter
+ Vi kontaktar dig eftersom du har publicerat produkter som du måste skicka in dokument om överensstämmelse för.
+ Produktposterna saknar dokument om överensstämmelse
+ Hej!
+ Vi kontaktar dig eftersom du har publicerat produkter för vilka du måste skicka in dokument om överensstämmelse. Klicka på Granska krav på överensstämmelse nedan om du vill visa listan med berörda produkter och skicka sedan in de dokument om överensstämmelse som krävs. Om du inte skickar in dokumenten senast det angivna förfallodatumet för respektive produkt i den här länken, så kan vi komma att ta bort de berörda produktposterna.
+ Visa krav på överensstämmelse
+ I tabellen nedan visas en av dina berörda produktposter som exempel. Klicka på Granska krav på överensstämmelse om du vill se alla dina berörda produktposter.
+ SKU ASIN Status WHEUSGMH81901 B0DD7R3PPG Riskerar borttagning
+ Varför händer det här?
+Det här kravet hjälper till att säkerställa att produkterna är säkra för kunderna och överensstämmer med lokala lagar.
+ Vad behöver jag göra om jag vill fortsätta att sälja de här produkterna?
+Klicka på Granska krav på överensstämmelse om du vill ha m</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Rispondi ai requisiti di conformità per le tue offerte</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>96
+Azione richiesta: Informazioni importanti sulle sue offerte
+ La contattiamo perché ha pubblicato offerte di prodotti che richiedono l'invio di documenti di conformità.
+ Le offerte dei prodotti sono prive dei documenti di conformità obbligatori
+ Buongiorno,
+ ti contattiamo perché hai pubblicato offerte di prodotti che richiedono l'invio di documenti di conformità. Clicca su Visualizza requisiti di conformità qui sotto per accedere all'elenco dei prodotti interessati e inviare i documenti di conformità richiesti. Se non invierai i documenti entro il termine indicato per ciascun prodotto, le offerte di tali prodotti potrebbero essere rimosse.
+ Visualizza requisiti di conformità
+ La tabella seguente contiene un campione delle offerte interessate. Clicca su Visualizza requisiti di conformità per accedere all'elenco completo.
+ SKU ASIN Stato delle offerte WHEUSGMH81901 B0DD7R3PPG A rischio di rimozione
+ Perché succede questo?
+L'aderenza ai requisiti contribuisce a garantire che i prodotti siano conformi alle leggi locali e non rappresentino un rischio per i clienti.
+ Come faccio a continuare a vendere i prodotti interessati?
+Clicca su Visualizza requisiti di conformità per ottenere ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 5 Mar 2026 20:11:29 +0000</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to avoid listing deactivation</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai EU,
+ Some of your listings are at risk of deactivation due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
+ For step-by-step instructions, see our Submit compliance documents or appeal a documentation request help page.
+ To avoid further impact to your account, close or delete any non-compliant listings that you do</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 28 Feb 2026 05:28:30 +0000</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Hantera efterlevnadskrav för dina produktposter</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>96
+Åtgärd krävs: Viktig information angående dina produktposter
+ Vi kontaktar dig eftersom du har publicerat produkter som du måste skicka in dokument om överensstämmelse för.
+ Produktposterna saknar dokument om överensstämmelse
+ Hej!
+ Vi kontaktar dig eftersom du har publicerat produkter för vilka du måste skicka in dokument om överensstämmelse. Klicka på Granska krav på överensstämmelse nedan om du vill visa listan med berörda produkter och skicka sedan in de dokument om överensstämmelse som krävs. Om du inte skickar in dokumenten senast det angivna förfallodatumet för respektive produkt i den här länken, så kan vi komma att ta bort de berörda produktposterna.
+ Visa krav på överensstämmelse
+ I tabellen nedan visas en av dina berörda produktposter som exempel. Klicka på Granska krav på överensstämmelse om du vill se alla dina berörda produktposter.
+ SKU ASIN Status K6-KGRL-T8E4 B0DYTPRM8Z Riskerar borttagning
+ Varför händer det här?
+Det här kravet hjälper till att säkerställa att produkterna är säkra för kunderna och överensstämmer med lokala lagar.
+ Vad behöver jag göra om jag vill fortsätta att sälja de här produkterna?
+Klicka på Granska krav på överensstämmelse om du vill ha me</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Feb 2026 08:54:27 +0000</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
+ DOC REVIEW</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Do not reply back to this e-mail!
+Hello,
+Thank you for submitting a document to the Chemical Safety Compliance Team.
+● The document uploaded for "B0FCDRNTT8" is incomplete, inaccurate or otherwise conflicting, and cannot be used for classification. Specifically:
+→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
+The SDS does not include the legislation/regulation in accordance with the document was created
+Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
+Once you have corrected the problems listed above, please re-upload a valid document in "Manage Your Compliance" on "Provide documents" section.
+For any questions/appeals regarding this product/other products, please submit them ( for each ASIN separately ) in "Manage Your Compliance" on the relevant Appeal reason:
+1. Go to the Performance tab and select Account health.
+2. Under Manage your compliance in the bottom right corner, click Product compliance requests.
+3. Click Add or appeal compliance button for the product you’re taking action on.
+4. To upload the documentation, drag and drop fil</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Feb 2026 05:31:26 +0000</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
+ For step-by-step instru</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 26 Feb 2026 21:23:05 +0000</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai CA,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
+ For step-by-step instruct</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 26 Feb 2026 15:18:58 +0000</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Seller News: February 2026</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services
+ 96
+ OTDR update, FBA removal and disposal charge change, 30-day SAFE-T claim window, and more.
+ Our Seller Newsletter provides the most important policy, tool, and program updates from the past month. Stay informed about selling on Amazon.
+ Update to OTDR listing deactivation process as of February 28
+ Effective February 28, 2026, we’ll update how we apply the existing 90% on-time delivery rate (OTDR) requirement for seller-fulfilled listings. Previously, if your OTDR fell below 90%, all of your seller-fulfilled listings would be deactivated. With this change, only the listings that have the most impact on your ratings drop will be deactivated. Read more .
+ FBA removal and disposal fees to be charged as units are processed
+ Effective March 1, Fulfillment by Amazon (FBA) removal and disposal fees will be charged on a per-unit basis at the time each unit is removed or disposed of. Previously, these fees were charged all at once when the entire removal or disposal order was completed. Read more .
+ US SAFE-T claim filing window changes to 30 days on Feb 16
+ Effective February 16, 2026, the SAFE-T claim filing window for US seller-fulfilled orders will change from 60 da</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 26 Feb 2026 09:56:14 +0000</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Seller News: February 2026</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services
+ 96
+ Create A+ Content with AI, digital services fee update, monitor business hour delivery rate, and more.
+ Our Seller Newsletter provides the most important policy, tool and programme updates from the past month. Stay informed about selling on Amazon.
+ Create A+ Content easily with generative AI tools
+ Generative AI tools in the A+ Content Manager are now available to all brand-registered sellers in your store. Now with our new AI capabilities, you can create this content in minutes instead of weeks. Read more .
+ Update to digital services fee starting March 20
+ Effective from March 20, 2026, we’ll update how the digital services fee is applied to sales in our France, Italy and Spain stores for sellers established outside these countries. Read more .
+ Amazon Multi-Channel Fulfilment Shopify app is live in the UK
+ Our Multi-Channel Fulfilment (MCF) Shopify app will be available to UK sellers to fulfil your Shopify orders using your existing Amazon inventory. By using a single pool of Amazon inventory across all of your sales channels, you can simplify operations without investing in additional fulfilment infrastructure. Read more .
+ Monitor your business hour deliv</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 26 Feb 2026 05:24:39 +0000</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
+ For step-by-step instru</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 21:13:50 +0000</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai CA,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
+ For step-by-step instruct</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 18:19:49 +0000</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
+ For step-by-step instru</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 11:03:26 +0000</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Submit UK import details by 26/04/2026 to avoid shipping
+ restrictions</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit UK import details by 26/04/2026 to avoid shipping restrictions
+ Hello Weihai EU,
+ Your Amazon.co.uk seller account requires Import Entry Numbers (IENs) for shipments to UK fulfilment centres. You must provide these details by 26/04/2026 to continue creating new UK shipments.
+ Why is this happening?
+ We are taking this action because we identified shipments to Amazon UK fulfilment centres without valid Import Entry Numbers (IENs). UK Customs authorities assign these IENs when goods are imported into the UK. As the seller, you must obtain these numbers from your customs declarant, logistics agent or freight forwarder to maintain UK shipping compliance .
+ Where do I enter my Import Entry Numbers (IEN)?
+ To enter the IENs for your applicable shipments:
+- Go to your Shipping Queue and identify shipments received in Amazon UK FCs.
+- Under “Status”, click the “Import details” text. It will open a pop-up, where you can enter the IENs corresponding to the relevant shipment. You must provide a valid IEN.
+- Save your IEN entry.
+ If you would need to update your IEN, you can follow the above steps again.
+ What happens if I don’t submit these details?
+ You have 60 days after first re</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 05:20:21 +0000</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
+ For step-by-step instru</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 24 Feb 2026 16:07:02 +0000</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Submit Product Safety Law compliance information for Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ You can now submit PSL compliance information through the listing workflow and Manage All Inventory.
+ Hello,
+ You can now submit Product Safety Law (PSL) compliance information through the listing workflow for new listings, or through Manage All Inventory for existing listings.
+ In November 2024, Saudi Arabia implemented the PSL, which applies to most consumer products sold in Saudi Arabia, except those regulated by the Saudi Food and Drug Authority (SFDA).
+ To ensure you’re compliant, we recommend that you submit the following information as soon as possible:
+- Email or URL of the manufacturer
+- Email or URL of the importer if applicable, or your authorized representative in Saudi Arabia
+- Safety information, warnings, safety images or disclaimers
+- Proof of your product’s compliance with applicable Saudi technical standards For more information, go to Product Safety Law (PSL) .
+ The Amazon Services team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 23 Feb 2026 20:18:57 +0000</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Hantera efterlevnadskrav för dina produktposter</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>96
+Åtgärd krävs: Viktig information angående dina produktposter
+ Vi kontaktar dig eftersom du har publicerat produkter som du måste skicka in dokument om överensstämmelse för.
+ Produktposterna saknar dokument om överensstämmelse
+ Hej!
+ Vi kontaktar dig eftersom du har publicerat produkter för vilka du måste skicka in dokument om överensstämmelse. Klicka på Granska krav på överensstämmelse nedan om du vill visa listan med berörda produkter och skicka sedan in de dokument om överensstämmelse som krävs. Om du inte skickar in dokumenten senast det angivna förfallodatumet för respektive produkt i den här länken, så kan vi komma att ta bort de berörda produktposterna.
+ Visa krav på överensstämmelse
+ I tabellen nedan visas en av dina berörda produktposter som exempel. Klicka på Granska krav på överensstämmelse om du vill se alla dina berörda produktposter.
+ SKU ASIN Status K6-KGRL-T8E4 B0DYTPRM8Z Riskerar borttagning
+ Varför händer det här?
+Det här kravet hjälper till att säkerställa att produkterna är säkra för kunderna och överensstämmer med lokala lagar.
+ Vad behöver jag göra om jag vill fortsätta att sälja de här produkterna?
+Klicka på Granska krav på överensstämmelse om du vill ha me</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 23 Feb 2026 17:12:51 +0000</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Submit product compliance documents to avoid listing removal</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product compliance documents to avoid listing removal
+ Hello Weihai US,
+ Your listings are at risk of removal due to missing Safety Data Sheets. Submit the required documentation by 2026-04-09 to continue selling these products. You can find examples of your at-risk listings at the bottom of this email.
+ Why is this happening?
+ We are taking this action because we identified hazardous products in your catalog that require Safety Data Sheets (SDS). These documents are required by law and provide critical safety information about chemical products, including proper handling, storage, and emergency procedures. This helps ensure the safety of our customers, employees, and anyone who handles these products.
+ To learn more, visit our Requirements and FAQ for the sale of chemicals .
+ How do I continue to sell the affected products?
+ To avoid listing removal and continue selling these products, upload the Safety Data Sheets (SDS) for each of the impacted products. Click the “View Compliance Requirements” button below to see all affected listings.
+ View Compliance Requirements
+ What was impacted?
+ Reason
+ At-risk sales
+ Roaxkois Paint Your Own Mug Set, Mother's Day Pottery Kit In</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 23 Feb 2026 17:10:23 +0000</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Submit product compliance documents to avoid listing removal</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product compliance documents to avoid listing removal
+ Hello Weihai CA,
+ Your listings are at risk of removal due to missing Safety Data Sheets. Submit the required documentation by 2026-04-09 to continue selling these products. You can find examples of your at-risk listings at the bottom of this email.
+ Why is this happening?
+ We are taking this action because we identified hazardous products in your catalogue that require Safety Data Sheets (SDS). These documents are required by law and provide critical safety information about chemical products, including proper handling, storage and emergency procedures. This helps ensure the safety of our customers, employees and anyone who handles these products.
+ To learn more, visit our Requirements and FAQ for the sale of chemicals .
+ How do I continue to sell the affected products?
+ To avoid listing removal and continue selling these products, upload the Safety Data Sheets (SDS) for each of the impacted products. Click the “View Compliance Requirements” button below to see all affected listings.
+ View Compliance Requirements
+ What was impacted?
+ Reason
+ At-risk sales
+ Paint Your Own Mug Set, Mother's Day Pottery Kit Includes Mu</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 23 Feb 2026 16:27:54 +0000</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Notificaciones automáticas de Amazon Seller Central (favor de no responder a este mensaje) &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Aborda los requisitos de cumplimiento para los listados</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>96
+Acción requerida: Información importante sobre tus listados de productos
+ Nos ponemos en contacto contigo ya que has publicado productos que requieren nos envíes documentos de cumplimiento normativo.
+ A los listados de productos les faltan documentos obligatorios de cumplimiento normativo
+ Hola:
+ Nos comunicamos contigo porque publicaste productos que requieren que envíes documentos de cumplimiento normativo. Haz clic en “Revisar requisitos de cumplimiento normativo” a continuación para consultar la lista de productos afectados y enviar los documentos de cumplimiento normativo obligatorios. Si no envías la documentación antes de la fecha de vencimiento indicada para cada producto en este enlace, es posible que se eliminen los listados afectados.
+ Revisar requisitos de cumplimiento normativo
+ La siguiente tabla contiene una muestra de los listados afectados. Haz clic en “Revisar requisitos de cumplimiento normativo” para consultar todos los listados afectados.
+ SKU ASIN Estado del listado 7N-0PZT-LEBX B0FCDRNTT8 Listados en riesgo de retiro
+ ¿A qué se debe?
+Este requisito ayuda a garantizar que los productos cumplan con las leyes locales y que sean seguros para los clientes.
+ ¿Có</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 18 Feb 2026 20:09:07 +0000</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to avoid listing deactivation</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+ Some of your listings are at risk of deactivation due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
+ For step-by-step instructions, see our Submit compliance documents or appeal a documentation request help page.
+ To avoid further impact to your account, close or delete any non-compliant listings that you do</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 17 Feb 2026 16:10:02 +0000</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
+ For step-by-step instru</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Worten Marketplace - Portugal y España</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>¡Buenos días!
+Espero que te encuentres bien.
+Mi nombre es Gabriel Martins y soy Business Developer en WORTEN Portugal y España, parte de Sonae, uno de los más grandes grupos empresariales en Portugal.
+Te envío este mensaje porque nos gustaría hacer una colaboración entre Weihai EU y el Marketplace de Worten.
+Sobre Worten.
+Somos líderes en el mercado portugués, con 200 tiendas alcanzamos más de 1.2 billones de euros en ventas, de los cuales el 20% vienen del online.
+En Portugal, Worten.pt es el sitio de comercio electrónico más visitado y con mejor desempeño, recibimos más visitas que los principales marketplaces del mundo, los que consideramos nuestra competencia. En compras online, el sitio web de Worten tiene el mayor tráfico de Portugal, más de 10 millones de visitas al mes.
+Es en www.worten.pt y www.worten.es donde puedes mirar nuestro Marketplace.
+Con más de 30 categorías, el Marketplace de Worten quiere ser la plataforma donde los clientes pueden encontrar todo lo que necesitan.
+Con la gran demanda que sentimos, tenemos la oportunidad de aumentar nuestra gama de productos, ¡y trabajar con las mejores empresas es nuestra prioridad !
+Worten Marketplace tiene una estrategia B2C,</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
+ Bands is still in your basket</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
+Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
+Spring Deal -15% £14.16 Was: £16.66
+https://www.amazon.co.uk/gp/product/B0DRCF83VZ/?ref_=
+View your basket
+https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
+Manage your preferences https://www.amazon.co.uk/gp/cpc/homepage?ref_=pe_ob_ftr_comm_prfs
+Unsubscribe https://www.amazon.co.uk/gp/gss/o/1.pmxVEqsT3gXrFh88fSyuCe6DI9uiuU4C0KKMhooAImAzSBJB.D2l6BmGyrhR2QU
+Amazon.co.uk is a trading name for Amazon EU Sarl, for Amazon Europe Core Sarl, and for Amazon Media EU Sarl, all of which have their registered office at 38 avenue John F. Kennedy, L-1855 Luxembourg. ©2026 Amazon.com, Inc. or its affiliates. Amazon and all related marks are trademarks of Amazon.com, Inc. or its affiliates. Shipping costs may apply. The price and availability displayed on amazon.co.uk at the time of purchase will apply to your purchase. Ref: 1253060271.
+Privacy Notice https://www.amazon.co.uk/gp/help/customer/display.html?nodeId=201909010
+Amazon.co.uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>春季促销日 2026：最后提报您促销活动的机会</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>立即规划您的促销
+尊敬的卖家：
+春季促销日已经开始！您仍然可以为高潜力商品提交 Prime专享价格折扣和优惠券。不要错过在此次春季购物活动中触达数百万顾客的最后机会。
+关键日期
+活动日期： 2026 年 3 月 10 - 16 日
+提交截止日期： 活动结束前 12 小时
+即刻提报您的促销活动
+优惠券 &gt; https://go.amazonsellerservices.com/e/229492/oupon-ld-DC-EM-D403389586-Wk11/7z24pyz/6548637104/h/o6MODTBWFOoJ-lTgG6jkhHwTY0UdhKXkfXm7u4fY9qo
+价格折扣 &gt;https://go.amazonsellerservices.com/e/229492/reate-ld-DC-EM-D403389586-Wk11/7z24pz3/6548637104/h/o6MODTBWFOoJ-lTgG6jkhHwTY0UdhKXkfXm7u4fY9qo
+您的 ASIN 推荐清单
+以下为您精选了一批适合提报春季促销日活动的推荐 ASIN。
+&lt;div style="padding: 0 20px; "&gt;&lt;table style="width:100%; border-collapse:collapse; text-align:center; font-family:Amazon Ember Display, Arial, sans-serif; border:2px solid #868D95; border-radius:10px 10px 0 0; overflow:hidden; "&gt;&lt;thead&gt;&lt;tr style="background-color:#dfdad5;"&gt;&lt;th style="padding:10px; border-right:2px solid #868D95; font-size:14px; letter-spacing:none; line-height:1.2; text-align:center; mso-line-height-alt:1.063em; color:#000000;"&gt;站点&lt;/th&gt;&lt;th style="padding:10px; border-right:2px solid #868D95; font-size:14px; letter-spacing:none; line-height:1.2; text-align:center; mso-line-height-alt:1.063em; color:#000000;"&gt;ASIN&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="padding:10px; border-top:2px solid #868D9</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 9 Mar 2026 15:38:05 +0000</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 2/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 2/2026)</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.ca
+ Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
+Nous vous écrivons pour vous informer que votre Facture Expédié Par Amazon pour le mois de 2/2026 est maintenant disponible dans votre compte Seller Central.
+Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
+Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
+Pour toute question, contactez le Support Vendeur.
+Cordialement,
+Amazon.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 9 Mar 2026 11:10:45 +0000</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Worten Marketplace - Portugal y España</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Hola Weihai EU,
+Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
+Nuestro equipo de análisis ha señalado que una asociación con usted sería una gran oportunidad para ambos.
+¿Estaría disponible para una reunión online esta semana?
+Acerca de Worten - Somos el líder del mercado portugués:
+- Nº 1 del comercio electrónico portugués
+- Sitio web con mayor tráfico de Portugal (más de 10 millones de visitas al mes) - Ranking de mercado
+- Más de 200 tiendas físicas en Portugal y España, proporcionando una oportunidad omnicanal
+- Plataforma de gestión: Mirakl (se puede integrar manualmente o vía API)
+- Sin costes iniciales - 6 meses
+Estaré encantado de ayudarle si tiene alguna pregunta.
+Muchas gracias,
+Saludos Cordiales</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 7 Mar 2026 01:02:00 +0000</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.co.uk Merchant Credit Note for 2/2026</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Merchant Credit Note for the month of 2/2026 is now available in your Seller Central Account.
+To access your credit note, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your credit note.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.co.uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 23:28:03 +0000</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 2.2026</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnungskorrektur) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnungskorrektur) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 23:16:57 +0000</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Je Creditnota Verkoper Amazon.nl voor 2/2026</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
+We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
+Als je toegang wilt krijgen tot je creditnota, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
+In je Seller Central-account kun je je creditnota bekijken, downloaden of afdrukken.
+Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
+Met vriendelijke groeten,
+Amazon.nl</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 23:10:12 +0000</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 2.2026</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnungskorrektur) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnungskorrektur) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 22:15:50 +0000</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 21:01:28 +0000</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Amazon.pl – Faktura Realizacja przez Amazon za 2 2026</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
+Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 2 i rok 2026.
+Aby uzyskać dostęp do tego dokumentu typu faktura, przejdź na konto Seller Central &gt; Raporty &gt; Dokumenty podatkowe &gt; Faktury podatkowe z tytułu opłat od sprzedawcy.
+Na koncie Seller Central możesz wyświetlić, pobrać i wydrukować taki dokument (faktura).
+Jeśli masz jakieś pytania, skontaktuj się z działem pomocy dla sprzedawców.
+Pozdrawiamy,
+Amazon.pl</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 20:56:07 +0000</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
+Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
+För att komma åt ditt fakturagår du till ditt Seller Central-konto &gt; Rapporter &gt; Bibliotek för skattedokument &gt; Skattefakturor för säljaravgifter.
+På ditt Seller Central-konto kan du se, ladda ner eller skriva ut ditt faktura.
+Om du har några frågor, kontakta säljarsupport.
+Vänliga hälsningar,
+Amazon.se</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 20:28:14 +0000</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 2/2026</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.ie</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 20:17:57 +0000</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hola, Weihai EU:
+ Algunos de tus listings están en riesgo de desactivación debido a que tus productos no cumplen los requisitos obligatorios. Revisa a continuación los detalles y siguientes pasos. Los listings afectados aparecen al final de este correo electrónico.
+ ¿A qué se debe esto?
+ Tomamos esta medida porque a estos productos les falta información de cumplimiento normativo obligatoria. Para más información sobre las leyes, normativas y políticas de Amazon aplicables, consulta Cumplimiento y seguridad de los productos .
+ En la tabla que aparece al final de este correo electrónico se proporcionan los requisitos de cumplimiento normativo específicos del producto.
+ ¿Cómo puedo reactivar mis listings?
+ Para proporcionar la información de cumplimiento normativo obligatoria, ve a la página Estado de la cuenta y localiza las solicitudes de cumplimiento normativo del producto:
+-
+ Si dispones de la documentación obligatoria, sigue las instrucciones para presentar los documentos de cumplimiento normativo.
+-
+ Si crees que tus productos están exentos de estos requisitos, presenta documentación que demuestre por qué no están sujetos a estos requisitos de cumplimiento normativo.
+ Para v</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 20:17:26 +0000</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>提交商品安全文件以避免商品被停售</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ 尊敬的 Weihai EU：
+您好！
+ 您的部分商品因缺少必要的商品合规信息而面临被停售的风险。查看下面的详细信息和后续步骤。受影响的商品显示在此电子邮件的末尾。
+ 为什么会发生这种情况？
+ 我们之所以采取此措施，是因为这些商品缺少必要的合规信息。请查看我们的 商品安全与合规 帮助页面，了解有关适用法律法规和亚马逊政策的信息。
+ 此电子邮件末尾的表格提供了特定于商品的合规性要求。
+ 如何重新启售商品？
+ 要提供所需的合规信息，请前往 账户状况 页面并找到商品合规性请求：
+-
+ 如果您有所需的文件，请按照相关说明提交您的合规文件。
+-
+ 如果您认为您的商品无需遵守这些要求，请提交相关文件，说明它们为何不受这些合规要求的约束。
+ 有关分步操作说明，请参阅 提交合规文件或对文件请求提出申诉 帮助页面。
+ 为避免进一步影响您的账户，请停售或删除您不打算销售或申诉的任何不合规商品。
+ 如果我未执行上述操作，会怎么样？
+ 如果您未在“账户状况”页面显示的截止日期之前提供所需的合规信息，我们可能会停售受影响的商品。
+ 我们愿意随时为您提供帮助。
+ 有关更多信息，请观看卖家大学中的 安全与合规简介 视频
+ 如果您有其他问题，请在您的 账户状况 控制面板上提交请求。
+ 亚马逊商品安全与合规性
+ 受影响的商品
+ 详情
+ Roaxkois Töpferset für Kinder, Töpferset für Zuhause mit ton lufttrocknend, Töpferscheibe Elektrisch, Diamant Aufkleber, Kreativ Set für Kinder, Geschenk-Ideen, Geschenk für Mädchen Jungen
+ ASIN： B0DL3PC2WS
+ 亚马逊要求您证明自己在亚马逊德国站上架的儿童玩具符合适用的法律、法规、标准和亚马逊政策。
+要销售儿童玩具，您必须满足 儿童玩具帮助页面 上列出的要求，并与我们的合作伙伴第三方测试、检验和认证 (TIC) 服务提供商合作，验证您的商品符合这些要求。
+儿童玩具是指供14岁或以下儿童在学习或玩耍时使用的商品。
+亚马逊根据以下标准来确定商品是否为“儿童玩具”：
+商品包装上的年龄分级标明该玩具专供 14 岁或以下儿童使用。
+产品的包装、展示、促销或广告显示该产品适合 14 岁或以下儿童使用。
+消费者通常认为该商品供 14 岁或以下儿童使用。
+有关合规要求、如何与 TIC 服务提供商合作的更多信息，或者要观看有关本政策涵盖的儿童玩具的视频，请访问 儿童玩具帮助页面 。
+ 报告此电子邮件的问题
+ 如果您有任何问题，请访问: Seller Central
+ 要更改您的电子邮件首选项，请访问： 通知首选项
+ 2026 Amazon.com 旗下公司 保留所有权利
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 20:15:57 +0000</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Dzień dobry Weihai EU,
+ niektóre z Twoich ofert są zagrożone dezaktywacją z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
+ Dlaczego tak się stało?
+ Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami .
+ Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
+ Jak mogę ponownie aktywować oferty?
+ Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i znajdź żądania dotyczące zgodności produktu z wymogami:
+-
+ Jeśli dysponujesz wymaganymi dokumentami zgodności, postępuj zgodnie z instrukcjami, aby je przesłać.
+-
+ Jeśli uważasz, że Twoje produkty są zwolnione z wymogów dotyczących zgodności, prześlij d</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 20:15:27 +0000</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Dien productveiligheidsdocumentatie in om de deactivering van de
+ productvermelding te voorkomen</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hallo Weihai EU,
+ Enkele van je productvermeldingen lopen het risico op deactivering omdat er verplichte nalevingsvereisten voor je producten ontbreken. Bekijk de gegevens en de stappen hieronder. De betreffende productvermeldingen worden aan het einde van deze e-mail weergegeven.
+ Waarom gebeurt dit?
+ We hebben deze actie ondernomen omdat voor deze producten verplichte nalevingsinformatie ontbreekt. Raadpleeg onze hulp-pagina Productveiligheid en -conformiteit voor informatie over de toepasselijke wet- en regelgeving en het Amazon-beleid.
+ De tabel aan het einde van deze e-mail bevat productspecifieke nalevingsvereisten.
+ Hoe activeer ik mijn productvermeldingen opnieuw?
+ Als je de vereiste nalevingsgegevens wilt verstrekken, ga je naar de pagina Accountstatus en zoek je de aanvragen voor productconformiteit:
+-
+ Als je over de vereiste documentatie beschikt, volg je de instructies om je nalevingsdocumenten in te dienen.
+-
+ Als je van mening bent dat je producten zijn vrijgesteld van deze vereisten, dien dan documentatie in waaruit blijkt wat de reden is dat ze niet aan deze nalevingsvereisten zijn onderworpen.
+ Raadpleeg voor stapsgewijze instructies onze hulp-pagina Documente</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 20:12:48 +0000</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hej Weihai EU!
+ Vissa av dina produktposter riskerar att inaktiveras på grund av att det saknas obligatorisk information om överensstämmelse för produkterna. Granska informationen och följande steg nedan. De berörda produktposterna visas i slutet av det här e-postmeddelandet.
+ Varför händer det här?
+ Vi vidtar den här åtgärden eftersom det saknas obligatorisk information om överensstämmelse för de här produkterna. Läs vår hjälpsida för Produktsäkerhet och -överensstämmelse för information om tillämpliga lagar, förordningar och Amazons policyer.
+ Tabellen i slutet av detta e-postmeddelande innehåller produktspecifika krav för överensstämmelse.
+ Hur återaktiverar jag mina produktposter?
+ Om du vill tillhandahålla den begärda överensstämmelseinformationen går du till sidan Kontostatus och letar upp begäranden om produktöverensstämmelse:
+-
+ Om du har den obligatoriska dokumentationen ska du skicka in dina överensstämmelsedokument enligt instruktionerna.
+-
+ Om du tror att dina produkter är undantagna från dessa krav skickar du in dokumentation som visar varför de inte omfattas av dessa överensstämmelsekrav.
+ Du hittar stegvisa instruktioner på vår hjälpsida om Skicka in intyg om öve</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 20:07:18 +0000</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.co.uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 20:02:17 +0000</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 2.2026</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 20:02:06 +0000</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 2/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 2/2026)</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
+We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
+Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
+In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
+Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
+Met vriendelijke groeten,
+Amazon.com.be
+ Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
+Nous vous écrivons pour vous informer que votre Facture Expédié Par Amazon pour le mois de 2/2026 est maintenant disponible dans votre compte Seller Central.
+Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
+Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
+Pour toute question, contactez le Support Vendeur.
+Cordialement,
+Amazon.com.be</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 19:35:00 +0000</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 2/2026</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 2/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.co.uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 19:32:44 +0000</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 19:24:20 +0000</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Je Factuur Verkoper Amazon.nl voor 2/2026</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
+We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
+Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
+In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
+Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
+Met vriendelijke groeten,
+Amazon.nl</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 18:55:05 +0000</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 18:24:37 +0000</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.co.uk Merchant Invoice for 2/2026</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.co.uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 17:58:56 +0000</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
+We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
+Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
+In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
+Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
+Met vriendelijke groeten,
+Amazon.nl</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 17:48:50 +0000</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.ie Merchant Invoice for 2/2026</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.ie</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 17:11:22 +0000</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 2.2026</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 16:54:03 +0000</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.co.uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 16:44:53 +0000</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Je Factuur Verkoper Amazon.com.be voor 2/2026 (Votre Facture
+ Vendeur Amazon.com.be pour le mois de 2/2026)</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
+We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
+Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
+In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
+Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
+Met vriendelijke groeten,
+Amazon.com.be
+ Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
+Nous vous écrivons pour vous informer que votre Facture Vendeur pour le mois de 2/2026 est maintenant disponible dans votre compte Seller Central.
+Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
+Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
+Pour toute question, contactez le Support Vendeur.
+Cordialement,
+Amazon.com.be</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 16:38:12 +0000</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
+We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
+Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
+In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
+Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
+Met vriendelijke groeten,
+Amazon.nl</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 16:28:10 +0000</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>La tua Fattura Elettronica Amazon Marketing Service Amazon.it per
+ 2/2026</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Gentile Shen zhen shi wei hai zhong xin ke ji you xian,
+Ti informiamo che la tua Fattura Elettronica Amazon Marketing Service per il mese di 2/2026 è ora disponibile sul tuo account di Seller Central.
+Per visualizzare la tua fattura, vai sul tuo Account Seller Central &gt; Report &gt; Documentazione fiscale &gt; "Fatture delle commissioni addebitate al venditore".
+Dall’account Seller Central potrai visualizzare, scaricare o stampare la tua fattura.
+Per qualsiasi domanda, contatta il Support al venditore.
+Distinti saluti,
+Amazon.it</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 16:09:11 +0000</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Din Faktura Säljare Amazon.se för 2/2026</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
+Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
+För att komma åt ditt fakturagår du till ditt Seller Central-konto &gt; Rapporter &gt; Bibliotek för skattedokument &gt; Skattefakturor för säljaravgifter.
+På ditt Seller Central-konto kan du se, ladda ner eller skriva ut ditt faktura.
+Om du har några frågor, kontakta säljarsupport.
+Vänliga hälsningar,
+Amazon.se</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 15:32:33 +0000</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.sa Fulfillment by Amazon Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) لتاجر Fulfilment by Amazon الخاصة بك لشهر 2/2026)</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.sa
+ عزيزي Shen zhen shi wei hai zhong xin ke ji you xian،
+نراسلك لإبلاغك بأن فاتورة ضريبة القيمة المضافة (VAT) لتاجر Fulfilment by Amazon الخاص بك لشهر 2/2026 متاح الآن في حساب Seller Central الخاص بك.
+للوصول إلى فاتورة الخاص بك، انتقل إلى حساب Seller Central الخاص بك &gt; التقارير &gt; مكتبة المستندات الضريبية &gt; فواتير ضريبة رسم البائع.
+في حساب Seller Central الخاص بك، ستتمكن من عرض {documentType}$ الخاص بك أو تنزيله أو طباعته.
+إذا كانت لديك أي أسئلة، فالمرجو التواصل مع دعم البائع.
+ مع أطيب التحيات،
+Amazon.sa</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 15:13:19 +0000</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
+Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
+För att komma åt ditt fakturagår du till ditt Seller Central-konto &gt; Rapporter &gt; Bibliotek för skattedokument &gt; Skattefakturor för säljaravgifter.
+På ditt Seller Central-konto kan du se, ladda ner eller skriva ut ditt faktura.
+Om du har några frågor, kontakta säljarsupport.
+Vänliga hälsningar,
+Amazon.se</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 14:56:47 +0000</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.sa Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 2/2026)</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.sa
+ عزيزي Shen zhen shi wei hai zhong xin ke ji you xian،
+نراسلك لإبلاغك بأن فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاص بك لشهر 2/2026 متاح الآن في حساب Seller Central الخاص بك.
+للوصول إلى فاتورة الخاص بك، انتقل إلى حساب Seller Central الخاص بك &gt; التقارير &gt; مكتبة المستندات الضريبية &gt; فواتير ضريبة رسم البائع.
+في حساب Seller Central الخاص بك، ستتمكن من عرض {documentType}$ الخاص بك أو تنزيله أو طباعته.
+إذا كانت لديك أي أسئلة، فالمرجو التواصل مع دعم البائع.
+ مع أطيب التحيات،
+Amazon.sa</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 14:29:22 +0000</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Amazon.pl – Faktura Sprzedawcy za 2 2026</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
+Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 2 i rok 2026.
+Aby uzyskać dostęp do tego dokumentu typu faktura, przejdź na konto Seller Central &gt; Raporty &gt; Dokumenty podatkowe &gt; Faktury podatkowe z tytułu opłat od sprzedawcy.
+Na koncie Seller Central możesz wyświetlić, pobrać i wydrukować taki dokument (faktura).
+Jeśli masz jakieś pytania, skontaktuj się z działem pomocy dla sprzedawców.
+Pozdrawiamy,
+Amazon.pl</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 11:10:20 +0000</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Worten Marketplace - Portugal y España</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>¡Buenos días!
+Espero que te encuentres bien.
+Mi nombre es Gabriel Martins y soy Business Developer en WORTEN Portugal y España, parte de Sonae, uno de los más grandes grupos empresariales en Portugal.
+Te envío este mensaje porque nos gustaría hacer una colaboración entre Weihai EU y el Marketplace de Worten.
+Sobre Worten.
+Somos líderes en el mercado portugués, con 200 tiendas alcanzamos más de 1.2 billones de euros en ventas, de los cuales el 20% vienen del online.
+En Portugal, Worten.pt es el sitio de comercio electrónico más visitado y con mejor desempeño, recibimos más visitas que los principales marketplaces del mundo, los que consideramos nuestra competencia. En compras online, el sitio web de Worten tiene el mayor tráfico de Portugal, más de 10 millones de visitas al mes.
+Es en www.worten.pt y www.worten.es donde puedes mirar nuestro Marketplace.
+Con más de 30 categorías, el Marketplace de Worten quiere ser la plataforma donde los clientes pueden encontrar todo lo que necesitan.
+Con la gran demanda que sentimos, tenemos la oportunidad de aumentar nuestra gama de productos, ¡y trabajar con las mejores empresas es nuestra prioridad !
+Worten Marketplace tiene una estrategia B2C,</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 5 Mar 2026 21:11:42 +0000</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
+ disattivazione dell'offerta</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Gentile Weihai EU,
+ Alcune delle tue offerte sono a rischio di disattivazione perché i relativi prodotti non soddisfano i requisiti obbligatori sulla conformità. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
+ Ciò a cosa è dovuto?
+ Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili.
+ La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
+ Come faccio a riattivare le mie offerte?
+ Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
+-
+ Se disponi della documentazione richiesta, segui le istruzioni per inviare i documenti di conformità.
+-
+ Se ritieni che i tuoi prodotti siano esenti da questi requisiti, invia la documentazione che dimostra il motivo per cui non sono soggetti a questi requisiti di conformità.
+ Per istruzioni dettagliate, consulta l</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 5 Mar 2026 21:08:11 +0000</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Bonjour Weihai EU,
+ Certaines de vos mises en vente risquent d’être désactivées, car vos produits ne respectent pas les exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
+ Pourquoi cela se produit-il ?
+ Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables.
+ Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
+ Comment réactiver mes produits mis en vente ?
+ Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
+-
+ Si vous disposez des documents requis, suivez les instructions pour soumettre vos documents de conformité.
+-
+ Si vous pensez que vos produits sont exemptés de ces exigences, soumettez des pièces justificatives prouvant les raisons pour lesquelles ils ne sont pas soumis à ces exigences de conformité.
+ Pour des instru</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 5 Mar 2026 20:28:32 +0000</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Spełnij wymogi zgodności dotyczące Twoich ofert</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>96
+Wymagane działanie: Ważna informacja dotycząca Twoich ofert produktów
+ kontaktujemy się z Tobą, ponieważ wystawiasz produkty, dla których niezbędne jest złożenie dokumentów potwierdzających zgodność z wymogami.
+ Do ofert produktów brakuje obowiązkowych dokumentów dotyczących zgodności z wymogami
+ Dzień dobry,
+ kontaktujemy się z Tobą, ponieważ wystawiasz produkty, dla których niezbędne jest przedłożenie dokumentów potwierdzających zgodność z wymogami. Kliknij opcję „Wyświetl wymagania dotyczące zgodności z wymogami” poniżej, aby wyświetlić listę produktów, których dotyczy problem, i przesłać wymagane dokumenty potwierdzające zgodność z wymogami. Jeśli nie prześlesz dokumentów w terminie wskazanym dla każdego produktu na tej stronie, możemy usunąć oferty, których dotyczy problem.
+ Wyświetl wymagania dotyczące zgodności z wymogami
+ Poniższa tabela zawiera przykłady ofert, których dotyczy problem. Kliknij pozycję „Wyświetl wymagania dotyczące zgodności z wymogami”, aby zobaczyć wszystkie oferty, których dotyczy problem.
+ SKU ASIN Status oferty WHEUSGMH81901 B0DD7R3PPG Zagrożone usunięciem
+ Skąd wynikła ta sytuacja?
+Wymóg ten pomaga zagwarantować, że produkty są zgodne z miejscowymi</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 5 Mar 2026 20:28:29 +0000</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Aborda los requisitos de cumplimiento de tus listings</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>96
+Toma medidas: Información importante sobre tus listings de producto
+ Nos ponemos en contacto contigo porque has publicado productos que requieren que aportes documentación sobre cumplimiento.
+ Listings de producto a los que les falta la documentación sobre cumplimiento solicitada
+ Hola:
+ Nos ponemos en contacto contigo porque has publicado productos que requieren que aportes documentación sobre cumplimiento. Haz clic en "Revisar requisitos de cumplimiento" a continuación para ver la lista de productos en cuestión y enviar la documentación sobre cumplimiento solicitada. Si no envías la documentación dentro del plazo indicado para cada producto en este enlace, es posible que eliminemos los listings afectados.
+ Revisar requisitos de cumplimiento
+ La tabla siguiente contiene una muestra de los listings afectados. Haz clic en "Revisar requisitos de cumplimiento" para ver todos los listings afectados.
+ SKU ASIN Estado del listing WHEUSGMH81901 B0DD7R3PPG En riesgo de retirada
+ ¿A qué se debe esto?
+Con este requisito nos aseguramos de que los productos cumplan con la legislación local y de que sean seguros para los clientes.
+ ¿Cómo puedo seguir vendiendo los productos afectados?
+Haz cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 5 Mar 2026 20:16:47 +0000</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>提交商品安全文件以避免商品被停售</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>96
+ 尊敬的 Weihai EU：
+您好！
+ 您的部分商品因缺少必要的商品合规信息而面临被停售的风险。查看下面的详细信息和后续步骤。受影响的商品显示在此电子邮件的末尾。
+ 为什么会发生这种情况？
+ 我们之所以采取此措施，是因为这些商品缺少必要的合规信息。请查看我们的 商品安全与合规 帮助页面，了解有关适用法律法规和亚马逊政策的信息。
+ 此电子邮件末尾的表格提供了特定于商品的合规性要求。
+ 如何重新启售商品？
+ 要提供所需的合规信息，请前往 账户状况 页面并找到商品合规性请求：
+-
+ 如果您有所需的文件，请按照相关说明提交您的合规文件。
+-
+ 如果您认为您的商品无需遵守这些要求，请提交相关文件，说明它们为何不受这些合规要求的约束。
+ 有关分步操作说明，请参阅 提交合规文件或对文件请求提出申诉 帮助页面。
+ 为避免进一步影响您的账户，请停售或删除您不打算销售或申诉的任何不合规商品。
+ 如果我未执行上述操作，会怎么样？
+ 如果您未在“账户状况”页面显示的截止日期之前提供所需的合规信息，我们可能会停售受影响的商品。
+ 我们愿意随时为您提供帮助。
+ 有关更多信息，请观看卖家大学中的 安全与合规简介 视频
+ 如果您有其他问题，请在您的 账户状况 控制面板上提交请求。
+ 亚马逊商品安全与合规性
+ 受影响的商品
+ 详情
+ Roaxkois Töpferscheibe, Mini-Töpferscheibe für Kinder, Töpferset für Zuhause mit ton lufttrocknend, Diamant Aufkleber
+ ASIN： B0DC9Y9JQJ
+ 亚马逊要求您证明自己在亚马逊德国站上架的儿童玩具符合适用的法律、法规、标准和亚马逊政策。
+要销售儿童玩具，您必须满足 儿童玩具帮助页面 上列出的要求，并与我们的合作伙伴第三方测试、检验和认证 (TIC) 服务提供商合作，验证您的商品符合这些要求。
+儿童玩具是指供14岁或以下儿童在学习或玩耍时使用的商品。
+亚马逊根据以下标准来确定商品是否为“儿童玩具”：
+商品包装上的年龄分级标明该玩具专供 14 岁或以下儿童使用。
+产品的包装、展示、促销或广告显示该产品适合 14 岁或以下儿童使用。
+消费者通常认为该商品供 14 岁或以下儿童使用。
+有关合规要求、如何与 TIC 服务提供商合作的更多信息，或者要观看有关本政策涵盖的儿童玩具的视频，请访问 儿童玩具帮助页面 。
+ Roaxkois Töpferscheibe, Mini-Töpferscheibe für Kinder, Töpferset für Zuhause mit ton lufttrocknend, Diamant Aufkleber
+ ASIN： B0DC9Y9JQJ
+ 亚马逊要求您证明自己在亚马逊德国站上架的儿童玩具符合适用的</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 5 Mar 2026 20:16:22 +0000</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hola, Weihai EU:
+ Algunos de tus listings están en riesgo de desactivación debido a que tus productos no cumplen los requisitos obligatorios. Revisa a continuación los detalles y siguientes pasos. Los listings afectados aparecen al final de este correo electrónico.
+ ¿A qué se debe esto?
+ Tomamos esta medida porque a estos productos les falta información de cumplimiento normativo obligatoria. Para más información sobre las leyes, normativas y políticas de Amazon aplicables, consulta Cumplimiento y seguridad de los productos .
+ En la tabla que aparece al final de este correo electrónico se proporcionan los requisitos de cumplimiento normativo específicos del producto.
+ ¿Cómo puedo reactivar mis listings?
+ Para proporcionar la información de cumplimiento normativo obligatoria, ve a la página Estado de la cuenta y localiza las solicitudes de cumplimiento normativo del producto:
+-
+ Si dispones de la documentación obligatoria, sigue las instrucciones para presentar los documentos de cumplimiento normativo.
+-
+ Si crees que tus productos están exentos de estos requisitos, presenta documentación que demuestre por qué no están sujetos a estos requisitos de cumplimiento normativo.
+ Para v</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 5 Mar 2026 20:12:51 +0000</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Dien productveiligheidsdocumentatie in om de deactivering van de
+ productvermelding te voorkomen</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hallo Weihai EU,
+ Enkele van je productvermeldingen lopen het risico op deactivering omdat er verplichte nalevingsvereisten voor je producten ontbreken. Bekijk de gegevens en de stappen hieronder. De betreffende productvermeldingen worden aan het einde van deze e-mail weergegeven.
+ Waarom gebeurt dit?
+ We hebben deze actie ondernomen omdat voor deze producten verplichte nalevingsinformatie ontbreekt. Raadpleeg onze hulp-pagina Productveiligheid en -conformiteit voor informatie over de toepasselijke wet- en regelgeving en het Amazon-beleid.
+ De tabel aan het einde van deze e-mail bevat productspecifieke nalevingsvereisten.
+ Hoe activeer ik mijn productvermeldingen opnieuw?
+ Als je de vereiste nalevingsgegevens wilt verstrekken, ga je naar de pagina Accountstatus en zoek je de aanvragen voor productconformiteit:
+-
+ Als je over de vereiste documentatie beschikt, volg je de instructies om je nalevingsdocumenten in te dienen.
+-
+ Als je van mening bent dat je producten zijn vrijgesteld van deze vereisten, dien dan documentatie in waaruit blijkt wat de reden is dat ze niet aan deze nalevingsvereisten zijn onderworpen.
+ Raadpleeg voor stapsgewijze instructies onze hulp-pagina Documente</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 5 Mar 2026 20:11:28 +0000</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Dzień dobry Weihai EU,
+ niektóre z Twoich ofert są zagrożone dezaktywacją z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
+ Dlaczego tak się stało?
+ Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami .
+ Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
+ Jak mogę ponownie aktywować oferty?
+ Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i znajdź żądania dotyczące zgodności produktu z wymogami:
+-
+ Jeśli dysponujesz wymaganymi dokumentami zgodności, postępuj zgodnie z instrukcjami, aby je przesłać.
+-
+ Jeśli uważasz, że Twoje produkty są zwolnione z wymogów dotyczących zgodności, prześlij d</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 5 Mar 2026 20:09:31 +0000</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hej Weihai EU!
+ Vissa av dina produktposter riskerar att inaktiveras på grund av att det saknas obligatorisk information om överensstämmelse för produkterna. Granska informationen och följande steg nedan. De berörda produktposterna visas i slutet av det här e-postmeddelandet.
+ Varför händer det här?
+ Vi vidtar den här åtgärden eftersom det saknas obligatorisk information om överensstämmelse för de här produkterna. Läs vår hjälpsida för Produktsäkerhet och -överensstämmelse för information om tillämpliga lagar, förordningar och Amazons policyer.
+ Tabellen i slutet av detta e-postmeddelande innehåller produktspecifika krav för överensstämmelse.
+ Hur återaktiverar jag mina produktposter?
+ Om du vill tillhandahålla den begärda överensstämmelseinformationen går du till sidan Kontostatus och letar upp begäranden om produktöverensstämmelse:
+-
+ Om du har den obligatoriska dokumentationen ska du skicka in dina överensstämmelsedokument enligt instruktionerna.
+-
+ Om du tror att dina produkter är undantagna från dessa krav skickar du in dokumentation som visar varför de inte omfattas av dessa överensstämmelsekrav.
+ Du hittar stegvisa instruktioner på vår hjälpsida om Skicka in intyg om öve</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 3 Mar 2026 11:10:25 +0000</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Worten Marketplace - Portugal y España</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Hola Weihai EU,
+Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
+Nuestro equipo de análisis ha señalado que una asociación con usted sería una gran oportunidad para ambos.
+¿Estaría disponible para una reunión online esta semana?
+Acerca de Worten - Somos el líder del mercado portugués:
+- Nº 1 del comercio electrónico portugués
+- Sitio web con mayor tráfico de Portugal (más de 10 millones de visitas al mes) - Ranking de mercado
+- Más de 200 tiendas físicas en Portugal y España, proporcionando una oportunidad omnicanal
+- Plataforma de gestión: Mirakl (se puede integrar manualmente o vía API)
+- Sin costes iniciales - 6 meses
+Estaré encantado de ayudarle si tiene alguna pregunta.
+Muchas gracias,
+Saludos Cordiales</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 3 Mar 2026 00:58:56 +0000</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>最后机会：请在3月9日前提报春季促销日的促销</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>3月9日前提报春季促销日促销
+尊敬的卖家，
+请于3月9日前提交Z划算和秒杀来参加2026 年春季促销日。请确保您的促销符合资格标准，以避免被系统禁止显示。
+关键日期
+活动日期： 2026年3月10日至3月16日
+提报截止日期： 2026年3月9日
+提报您的促销 &gt; https://go.amazonsellerservices.com/e/229492/reate-ld-DC-EM-P383172356-Wk10/7z1xvkb/6537507024/h/46C1UkBJwQ8NGdUxNRQae0WstMz1xGFMU-7p-Y5MlAk
+您的促销推荐
+以下是您春季促销日的ASIN推荐提报列表。 请在卖家中心促销仪表盘查看您的完整推荐列表，每周更新一次，为您提供新机会。
+&lt;div style="padding: 0 20px; "&gt;&lt;table style="width:100%; border-collapse:collapse; text-align:center; font-family:Amazon Ember Display, Arial, sans-serif; border:2px solid #868D95; border-radius:10px 10px 0 0; overflow:hidden; "&gt;&lt;thead&gt;&lt;tr style="background-color:#dfdad5;"&gt;&lt;th style="padding:10px; border-right:2px solid #868D95; font-size:14px; letter-spacing:none; line-height:1.2; text-align:center; mso-line-height-alt:1.063em; color:#000000;"&gt;站点&lt;/th&gt;&lt;th style="padding:10px; border-right:2px solid #868D95; font-size:14px; letter-spacing:none; line-height:1.2; text-align:center; mso-line-height-alt:1.063em; color:#000000;"&gt;ASIN&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="padding:10px; border-top:2px solid #868D95; border-right:2px solid #868D95; font-size:14px; letter-spacing:none; line-height:1.2; text-align:center; mso-line-height-alt:1.063em; color:</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 2 Mar 2026 21:40:34 +0000</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging
+Dear there,
+Thank you for being a valued member of the Amazon Multichannel Fulfillment (MCF) and Buy with Prime community. We are reaching out to make sure you have seen that starting in April 2026, MCF and Buy with Prime will introduce two updates to how orders are packaged and shipped in the United States:
+Packing slips will no longer be included by default.
+Items already certified for the Ships in Product Packaging (SIPP) program on Amazon.com will ship without an Amazon overbox by default.
+In addition, eligible MCF and Buy with Prime SIPP shipments will receive a discount. See the discounts table below for details: https://www2.amazonsupplychain.com/e/949422/inable-Packaging--FAQs--4--pdf/618lz1/1363808868/h/XBk-oWBas3G_VJ_7TyvkI7Rf5JXikqE4oRmyirpCbDA
+These updates support Amazon’s commitment to reducing packaging waste and align MCF and Buy with Prime more closely with existing Fulfillment by Amazon (FBA) packaging practices.
+What should I do?
+1. Learn more about SIPP for FBA https://www2.amazonsupplychain.com/e/949422/2026-03-02/618lz4/1363808868/h/XBk-oWBas3G_VJ_7TyvkI7Rf5JXikqE4oRmyirpCbDA and review the SIPP he</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 28 Feb 2026 11:10:30 +0000</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Worten Marketplace - Portugal y España</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>¡Buenos días!
+Espero que te encuentres bien.
+Mi nombre es Gabriel Martins y soy Business Developer en WORTEN Portugal y España, parte de Sonae, uno de los más grandes grupos empresariales en Portugal.
+Te envío este mensaje porque nos gustaría hacer una colaboración entre Weihai EU y el Marketplace de Worten.
+Sobre Worten.
+Somos líderes en el mercado portugués, con 200 tiendas alcanzamos más de 1.2 billones de euros en ventas, de los cuales el 20% vienen del online.
+En Portugal, Worten.pt es el sitio de comercio electrónico más visitado y con mejor desempeño, recibimos más visitas que los principales marketplaces del mundo, los que consideramos nuestra competencia. En compras online, el sitio web de Worten tiene el mayor tráfico de Portugal, más de 10 millones de visitas al mes.
+Es en www.worten.pt y www.worten.es donde puedes mirar nuestro Marketplace.
+Con más de 30 categorías, el Marketplace de Worten quiere ser la plataforma donde los clientes pueden encontrar todo lo que necesitan.
+Con la gran demanda que sentimos, tenemos la oportunidad de aumentar nuestra gama de productos, ¡y trabajar con las mejores empresas es nuestra prioridad !
+Worten Marketplace tiene una estrategia B2C,</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 28 Feb 2026 02:13:10 +0000</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>[Toma medidas] Proporciona más información en un plazo de 60 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Hola, Weihai EU:
+ Para cumplir nuestros requisitos de registro del impuesto sobre el valor añadido (IVA) europeo, necesitamos que nos proporciones más información.
+ ¿A qué se debe esto?
+ De acuerdo con nuestros requisitos de registro a efectos fiscales en Europa, tienes que proporcionarnos un número de identificación fiscal válido de todos los países en los que consideremos que tienes obligación de registrarte a efectos fiscales o confirmar el estado de registro en la Ventanilla Única del IVA (OSS) en tu país de origen.
+ Hemos detectado que tu cuenta tiene que cumplir una serie de requisitos para el registro a efectos fiscales en la Unión Europea, el Reino Unido, Noruega y Suiza, donde tienes la obligación de registrarte a efectos fiscales. En concreto, es posible que tengas que tomar medidas para lo siguiente:
+ Polonia
+ Para más información, consulta Información sobre el impuesto sobre el valor añadido (IVA) europeo .
+ ¿Cómo evito la desactivación de mi cuenta?
+ Para evitar la desactivación de la cuenta, consulta la sección "Acciones prioritarias" de la página Estado de la cuenta en los próximos 60 días. Desde ahí podrás hacer lo siguiente:
+- Revisar la información que tienes </t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 28 Feb 2026 02:09:55 +0000</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 60 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Dzień dobry Weihai EU,
+ potrzebujemy od Ciebie dodatkowych informacji, które pozwolą Ci spełnić europejskie wymagania Amazon dotyczące rejestracji jako podatnik VAT.
+ Dlaczego tak się stało?
+ Zgodnie z europejskimi wymaganiami Amazon dotyczącymi rejestracji jako podatnik VAT musisz podać nam ważny numer VAT dla wszystkich krajów, w których według nas podlegasz obowiązkowi rejestracji jako podatnik VAT, lub potwierdzenie statusu rejestracji w procedurze unijnej w Twoim kraju macierzystym.
+ Ustaliliśmy, że w przypadku Twojego konta w Unii Europejskiej, Zjednoczonym Królestwie, Norwegii i Szwajcarii, gdzie masz zobowiązania z tytułu VAT, istnieją wymogi w zakresie rejestracji jako podatnik VAT. Podjęcie działań może być w szczególności wymagane w następujących przypadkach:
+ Polska
+ Więcej informacji znajdziesz na stronie Informacje dotyczące podatku VAT w Europie .
+ Jak mogę zapobiec dezaktywacji konta?
+ Aby uniknąć dezaktywacji konta, w ciągu najbliższych 60 dni odwiedź sekcję „Działania priorytetowe” na stronie Kondycja konta . W sekcji tej można:
+- zweryfikować istniejące informacje dotyczące wymienionych krajów
+- przesłać informacje o VAT za pośrednictwem portali „Informacje o</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 28 Feb 2026 02:07:47 +0000</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>[Azione richiesta] Fornisci informazioni entro 60 giorni ed evita
+ la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Gentile Weihai EU,
+ Ai fini della conformità ai requisiti di registrazione IVA in Europa di Amazon, ti chiediamo di fornirci ulteriori informazioni.
+ Ciò a cosa è dovuto?
+ In base ai requisiti di registrazione IVA in Europa di Amazon, sei tenuto a fornirci un numero di partita IVA valido per tutti i paesi in cui riteniamo che tu abbia l'obbligo di effettuare tale registrazione o una conferma dello stato Union One-Stop Shop (OSS) relativo al tuo paese di registrazione.
+ Vi sono dei requisiti per la registrazione ai fini IVA che il tuo account deve soddisfare nei paesi in cui sei soggetto a obblighi in materia di IVA (stati dell'Unione europea, Regno Unito, Norvegia e Svizzera). Nello specifico, potrebbe essere necessario un intervento da parte tua per quanto segue:
+ Polonia
+ Per maggiori informazioni, consulta la pagina di aiuto Informazioni sull'IVA in Europa .
+ Come faccio a evitare la disattivazione dell'account?
+ Per evitare la disattivazione dell'account, visita entro i prossimi 60 giorni la sezione relativa alle azioni prioritarie della pagina Stato dell'account . Da qui, potrai effettuare le seguenti operazioni:
+- Verificare le informazioni esistenti per i paesi in elenco</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Feb 2026 18:30:15 +0000</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Tus límites de capacidad de Logística de Amazon para marzo</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Tus límites de capacidad de Logística de Amazon para marzo
+ Hola:
+ Se confirmaron tus límites de capacidad para el próximo periodo.
+ Pronóstico de capacidad para el periodo del mar. 1 al 31, a partir del feb. 26:
+ Tipo de almacenamiento
+ Límite de capacidad total (metros cúbicos)
+ Tamaño estándar
+ 16.42
+ Tamaño grande
+ 21.66
+ Para ver tus límites más actualizados, así como los límites de capacidad estimados para los dos meses siguientes, ve a los envíos de Logística de Amazon .
+ En la siguiente tabla, se muestra el uso de la capacidad de Logística de Amazon a partir del feb. 25.
+ Tipo de almacenamiento
+ Uso sin los envíos abiertos incluidos (metros cúbicos)
+ Uso con los envíos abiertos incluidos (metros cúbicos)
+ Tamaño estándar
+ 0.00
+ 0.00
+ Tamaño grande
+ 0.00
+ 0.00
+ Cómo se establecen los límites de capacidad de Logística de Amazon
+ Tus límites de capacidad dependen de tu puntuación del índice de desempeño de inventario y otros factores, como las proyecciones de ventas para tus ASIN, la capacidad del centro de distribución y el plazo de entrega de los envíos. Las estimaciones variarán en función de los cambios en tu puntuación del índice de desempeño de inventario y pueden au</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 19:18:58 +0000</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hej Weihai EU!
+ Vissa av dina produktposter har inaktiverats på grund av att det saknas obligatorisk överensstämmelse för dina produkter. Granska informationen och följande steg nedan. De berörda produktposterna visas i slutet av det här e-postmeddelandet.
+ Varför händer det här?
+ Vi vidtar den här åtgärden eftersom det saknas obligatorisk information om överensstämmelse för de här produkterna. Läs vår hjälpsida för Produktsäkerhet och -överensstämmelse för information om tillämpliga lagar, förordningar och Amazons policyer. Vi har använt oss av både automatiserade metoder och mänskliga expertgranskare för att identifiera problemet och fatta det här beslutet.
+ Tabellen i slutet av detta e-postmeddelande innehåller produktspecifika krav för överensstämmelse.
+ Hur återaktiverar jag mina produktposter?
+ Om du vill tillhandahålla den begärda överensstämmelseinformationen går du till sidan Kontostatus och letar upp begäranden om produktöverensstämmelse:
+-
+ Om du har den obligatoriska dokumentationen ska du skicka in dina överensstämmelsedokument enligt instruktionerna. Vi återaktiverar endast produkter som uppfyller kraven på överensstämmelse.
+-
+ Om du tror att dina produkter är und</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 19:18:56 +0000</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Dien productveiligheidsdocumentatie in om productvermeldingen
+ opnieuw te activeren</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hallo Weihai EU,
+ Sommige van je productvermeldingen zijn gedeactiveerd omdat er verplichte nalevingsvereisten voor je producten ontbreken. Bekijk de gegevens en de stappen hieronder. De betreffende productvermeldingen worden aan het einde van deze e-mail weergegeven.
+ Waarom gebeurt dit?
+ We hebben deze actie ondernomen omdat voor deze producten verplichte nalevingsinformatie ontbreekt. Raadpleeg onze hulp-pagina Productveiligheid en -conformiteit voor informatie over de toepasselijke wet- en regelgeving en het Amazon-beleid. We hebben gebruikgemaakt van een combinatie van geautomatiseerde middelen en deskundige menselijke beoordeling om dit probleem te identificeren en deze beslissing te nemen.
+ De tabel aan het einde van deze e-mail bevat productspecifieke nalevingsvereisten.
+ Hoe activeer ik mijn productvermeldingen opnieuw?
+ Als je de vereiste nalevingsgegevens wilt verstrekken, ga je naar de pagina Accountstatus en zoek je de aanvragen voor productconformiteit:
+-
+ Als je over de vereiste documentatie beschikt, volg je de instructies om je nalevingsdocumenten in te dienen. We zullen alleen producten herstellen die voldoen aan de nalevingsvereisten.
+-
+ Als je van mening ben</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 19:18:35 +0000</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Dzień dobry Weihai EU,
+ niektóre z Twoich ofert zostały zdezaktywowane z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
+ Dlaczego tak się stało?
+ Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami . Do identyfikacji problemu i podjęcia decyzji wykorzystaliśmy zautomatyzowane narzędzia, a otrzymane za ich pomocą wyniki poddaliśmy weryfikacji przez eksperta.
+ Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
+ Jak mogę ponownie aktywować oferty?
+ Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i znajdź żądania dotyczące zgodności produktu z wymogami:
+-
+ Jeśli dysponujesz wymaganymi dokument</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 19:13:40 +0000</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
+ le offerte</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Gentile Weihai EU,
+ Alcune delle tue offerte sono state disattivate a causa della mancanza di alcuni requisiti di conformità obbligatori per i tuoi prodotti. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
+ Ciò a cosa è dovuto?
+ Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili. Questa decisione è stata presa sulla base dei risultati di un'analisi effettuata in parte tramite revisione umana e in parte per mezzo di sistemi automatizzati.
+ La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
+ Come faccio a riattivare le mie offerte?
+ Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
+-
+ Se disponi della documentazione richiesta, segui le istruzioni per inviare i documenti di conformità. Ripristineremo solo i prodotti che soddisfano i requisiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 19:13:31 +0000</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Bonjour Weihai EU,
+ Certaines de vos mises en vente ont été désactivées, car vos produits ne respectaient pas des exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
+ Pourquoi cela se produit-il ?
+ Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables. Nous nous sommes appuyés sur une combinaison de moyens automatisés et de contrôles menés par des personnes expérimentées pour identifier ce problème et prendre cette décision.
+ Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
+ Comment réactiver mes produits mis en vente ?
+ Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
+-
+ Si vous disposez des documents requis, suivez les instructions pour soumettre vos documents de conformité. Nous rétablirons uniquement les produits</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 18:19:23 +0000</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hola, Weihai EU:
+ Algunos de tus listings se han desactivado debido a que tus productos no cumplen los requisitos obligatorios. Revisa a continuación los detalles y siguientes pasos. Los listings afectados aparecen al final de este correo electrónico.
+ ¿A qué se debe esto?
+ Tomamos esta medida porque a estos productos les falta información de cumplimiento normativo obligatoria. Para más información sobre las leyes, normativas y políticas de Amazon aplicables, consulta Cumplimiento y seguridad de los productos . Hemos usado una combinación de medios automatizados y revisión humana experta para identificar la incidencia y tomar una decisión.
+ En la tabla que aparece al final de este correo electrónico se proporcionan los requisitos de cumplimiento normativo específicos del producto.
+ ¿Cómo puedo reactivar mis listings?
+ Para proporcionar la información de cumplimiento normativo obligatoria, ve a la página Estado de la cuenta y localiza las solicitudes de cumplimiento normativo del producto:
+-
+ Si dispones de la documentación obligatoria, sigue las instrucciones para presentar los documentos de cumplimiento normativo. Sólo restableceremos los productos que cumplan los requisitos d</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 15:01:07 +0000</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Votre paiement est en cours</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Félicitations ! Votre paiement est en cours et arrivera sous peu.
+ Tentative de versement
+Félicitations, Weihai EU ! Votre paiement est en cours et arrivera sous trois à cinq jours.
+Le 02/25/26 15:00 CET, nous avons effectué un virement d’un montant de €
+ 119.06 sur le compte lié à votre méthode de paiement (compte bancaire se terminant par 229).
+ Si le montant est inférieur au montant auquel vous vous attendiez, voici quelques questions à vous poser :
+ Disposez-vous d’un solde de fonds non disponibles ? Amazon peut réserver des fonds afin de couvrir des retours, des réclamations ou des rétrofacturations potentiels des acheteurs. Si tel est le cas, le solde de fin de période de votre rapport sur les paiements affichera le solde des fonds non disponibles réservé.
+ Vos ventes couvraient-elles l’ensemble des frais et des retours pour cette période de règlements ? Le montant du paiement reflète votre activité commerciale, les frais de vente et les frais relatifs aux promotions et aux services. Nous vous recommandons de consulter votre rapport sur les paiements sous l’onglet Rapports de Seller Central pour comprendre votre solde de fin de pé</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 10:49:26 +0000</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Worten Marketplace - Portugal y España</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>Hola Weihai EU,
+Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
+Nuestro equipo de
+análisis ha señalado que una asociación con usted sería una gran oportunidad
+para ambos.
+¿Estaría
+disponible para una reunión online esta semana?
+Acerca de Worten
+- Somos el líder del mercado portugués:
+- Nº 1 del
+comercio electrónico portugués
+- Sitio web con
+mayor tráfico de Portugal (más de 10 millones de visitas al mes) - Ranking de mercado
+- Más de 200
+tiendas físicas en Portugal y España, proporcionando una oportunidad omnicanal
+- Plataforma de
+gestión: Mirakl (se puede integrar manualmente o vía API)
+- Sin costes los 6 meses iniciales
+Estaré encantado
+de ayudarle si tiene alguna pregunta.
+Muchas gracias,
+Saludos
+Cordiales</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 23 Feb 2026 17:09:03 +0000</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Envía documentos de cumplimiento normativo del producto para evitar que se retiren los listados</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Envía documentos de cumplimiento normativo del producto para evitar que se retiren los listados
+ Hola, Weihai MX:
+ Tus listados están en riesgo de ser retirados debido a que faltan las fichas de datos de seguridad (FDS). Envía la documentación obligatoria a más tardar el 2026-04-09 para seguir vendiendo estos productos. En la parte inferior de este correo electrónico, encontrarás ejemplos de listados en riesgo.
+ ¿A qué se debe?
+ Tomamos esta medida porque identificamos productos peligrosos en tu catálogo que requieren fichas de datos de seguridad (FDS). Estos documentos son obligatorios por ley y proporcionan información de seguridad importante sobre productos químicos, incluidos procedimientos de manipulación, almacenamiento y emergencia adecuados. Esto ayuda a garantizar la seguridad de nuestros clientes, empleados y cualquier persona que manipule estos productos.
+ Para más información, consulta los Requisitos y preguntas frecuentes para la venta de productos químicos .
+ ¿Cómo puedo seguir vendiendo los productos afectados?
+ Si quieres evitar el retiro de listados y seguir vendiendo estos productos, carga la ficha de datos de seguridad (FDS) de cada uno de los productos afect</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 19 Feb 2026 04:17:16 +0000</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Act today &amp; improve Sales on Excess Inventory</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Optional preview text
+ Hello,
+We noticed you have a number of ASIN(s) that have excess levels of inventory. We are reaching out to inform you about multiple options to improve your Unit Sales on your aged and/or excess inventory in Amazon Fulfillment Centers. Our goal is to help you increase the sales on this excess inventory:
+X004QEYPRL, X004MMFUYT, X004QEVV05
+We encourage you to take Amazon recommended actions such as Create Outlet deals, Sponsor Products Ad, to improve sell through of this excess inventory and potentially reduce your chances of incurring aged inventory fee.
+ Outlet deals
+ Amazon Outlet is a great place for customers to shop for overstock deals, which offers a selection of items, such as electronics, toys, beauty, and kitchen.
+ Create Outlet Deal Today!
+ Sponsored Product Ads
+ Sponsored Products is a cost-per-click advertising solution that provides advertisers with a foundation of controls and visibility to help get their individual products discovered, and help generate sales from traffic sources in the Amazon store and on select premium apps and websites.
+ Create Sponsored Products Ad Today!
+We encourage you to vie</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Create FBA removal order by 2026-03-26</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated removals of unfulfillable inventory
+ Required removals: First notification
+ Required removals: First notification
+ Hello,
+Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-03-26 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
+Unsellable products:
+- FNSKU: B0DRCF83VZ Quantity: 1
+- FNSKU: X002C14R1B Quantity: 1
+ Why is this happening?
+This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
+We leveraged a combination of automated means to identify this issue and make this decision.
+ How do I address this?
+Follow these steps to manage your unsellable inventory:
+- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
+- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
+ To avoid future manual inventory removal orders, set up Automated Unfulfillab</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 13:58:29 +0000</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Disposal order created for unsellable FBA inventory</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated Removals of Unfulfillable Inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Hello,
+You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
+ Why is this happening?
+This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
+ Removal order ID:
+- V8b2nNxJ7Y
+ Unsellable Products:
+- FNSKU: B0FD8RGZX3 Quantity: 1
+ For more information about the disposal order process, see Remove inventory from a fulfilment centre .
+ To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
+ The Fulfilment by Amazon Team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferen</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 13:29:25 +0000</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Disposal order created for unsellable FBA inventory</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated Removals of Unfulfillable Inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Hello,
+You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
+ Why is this happening?
+This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
+ Removal order ID:
+- FVSl6sGweZ
+ Unsellable Products:
+- FNSKU: X002A05YW5 Quantity: 2
+ For more information about the disposal order process, see Remove inventory from a fulfilment centre .
+ To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
+ The Fulfilment by Amazon Team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferen</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 3 Mar 2026 07:49:31 +0000</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>New removal fees for KSA apply starting March 30</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Effective March 30, 2026, removal fees will apply in the Kingdom of Saudi Arabia (KSA) for removals you initiate.
+ Hello,
+ Effective March 30, 2026, removal fees will apply in the Kingdom of Saudi Arabia (KSA) for removals you initiate. Amazon-initiated removals will continue to be free of charge.
+ This change helps maintain high-quality removal services while addressing increased operational costs in our fulfillment centers.
+ Until March 29, we'll continue processing all removal orders at no charge. After this date, fees will apply based on your product's size and weight:
+ Standard size
+- SAR 1.3 per unit (≤ 0.25 kg)
+- SAR 1.5 per unit (≤ 1 kg)
+- SAR 1.8 per unit (≤ 2 kg)
+- SAR 2 per unit (≤ 12 kg) Oversize
+- SAR 1.6 per unit (≤ 2 kg)
+- SAR 1.8 per unit (≤ 5 kg)
+- SAR 2 per unit (≤ 10 kg)
+- SAR 2.2 per unit (≤ 30 kg)
+- Additional SAR 0.5 per kg (over 30 kg) Thank you for your continued partnership. We remain committed to investing in programs to support your success in our store.
+ For more information, go to Remove inventory overview .
+ The Amazon Services team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences v</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Feb 2026 13:57:30 +0000</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Create FBA removal order by 2026-03-12</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated removals of unfulfillable inventory
+ Required removals: First notification
+ Required removals: First notification
+ Hello,
+Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-03-12 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
+Unsellable products:
+- FNSKU: X00265F4H9 Quantity: 1
+- FNSKU: X002C17O8J Quantity: 1
+ Why is this happening?
+This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
+We leveraged a combination of automated means to identify this issue and make this decision.
+ How do I address this?
+Follow these steps to manage your unsellable inventory:
+- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
+- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
+ To avoid future manual inventory removal orders, set up Automated Unfulfillab</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Feb 2026 12:08:33 +0000</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Disposal order created for unsellable FBA inventory</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated Removals of Unfulfillable Inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Hello,
+You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
+ Why is this happening?
+This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
+ Removal order ID:
+- uih6sNeVfd
+ Unsellable Products:
+- FNSKU: B0DRCF83VZ Quantity: 2
+- FNSKU: X002A05YW5 Quantity: 1
+ For more information about the disposal order process, see Remove inventory from a fulfilment centre .
+ To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
+ The Fulfilment by Amazon Team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferen</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 23 Feb 2026 13:32:21 +0000</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Stranded SKUs scheduled for automatic removal</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>96
+Stranded SKUs scheduled for automatic removal
+ Hello,
+ You are receiving this message because you have stranded inventory in an Amazon fulfilment centre that is scheduled for automatic removal. Stranded inventory is inventory without a buyable offer and requires you to either reactivate the listing or remove the inventory.
+ As of 2026-02-23, you have 1 new stranded SKUs scheduled for automatic removal, with the first 50 of these listed further below. You may have additional units scheduled for automatic removal from previous email notifications. For a full view of units scheduled for automatic removal, visit Fix stranded inventory and sort by Automatic Removal date .
+ Your inventory will be returned or disposed of based on the settings you selected on the Fix stranded inventory page. If you have not selected any settings, your inventory will be removed in 45 days from today’s date. To customise your settings, go to Fix stranded inventory and select Edit automatic-action settings .
+ If you need more time to appeal or fix a stranded inventory issue, go to Fix stranded inventory and select Delay removal for 30 days from the drop-down menu for each listing. Note: No additional notif</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 20 Feb 2026 13:43:58 +0000</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Disposal order created for unsellable FBA inventory</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated Removals of Unfulfillable Inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Hello,
+You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
+ Why is this happening?
+This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
+ Removal order ID:
+- DjHMcVqBnq
+ Unsellable Products:
+- FNSKU: X0025OLRH7 Quantity: 1
+- FNSKU: X0025UXT4F Quantity: 1
+- FNSKU: X002A05YW5 Quantity: 1
+ For more information about the disposal order process, see Remove inventory from a fulfilment centre .
+ To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
+ The Fulfilment by Amazon Team
+ Report an issue with this email
+ If you have any questions visit: Seller Centra</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 20 Feb 2026 13:32:50 +0000</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Create FBA removal order by 2026-03-05</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated removals of unfulfillable inventory
+ Required removals: First notification
+ Required removals: First notification
+ Hello,
+Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-03-05 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
+Unsellable products:
+- FNSKU: X002C17O8J Quantity: 1
+ Why is this happening?
+This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
+We leveraged a combination of automated means to identify this issue and make this decision.
+ How do I address this?
+Follow these steps to manage your unsellable inventory:
+- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
+- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
+ To avoid future manual inventory removal orders, set up Automated Unfulfillable Removals function in your FBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Envie os documentos de conformidade do produto para evitar a remoção da oferta
+ Olá, Weihai US.
+ Suas ofertas correm o risco de serem removidas devido à falta de Fichas de Informações de Segurança de Produtos Químicos. Envie a documentação necessária até 2026-04-09 para continuar vendendo esses produtos. Você pode encontrar exemplos de ofertas de produtos em risco na parte inferior deste e-mail.
+ Por que isso está acontecendo?
+ Estamos realizando tomando essa medida porque identificamos produtos perigosos em seu catálogo que exigem Fichas de Informações de Segurança de Produtos Químicos. Esses documentos são exigidos por lei e fornecem informações de segurança importantes sobre produtos químicos, incluindo procedimentos apropriados de manuseio, armazenamento e emergência. Isso ajuda a garantir a segurança de nossos clientes, funcionários e qualquer pessoa que venha a manusear esses produtos.
+ Para saber mais, acesse nossos Requisitos e perguntas frequentes sobre a venda de produtos químicos .
+ Como faço para continuar vendendo os produtos afetados?
+ Para evitar a remoção da oferta e continuar vendendo esses produtos, faça upload das Fichas de Informações de Segurança de Produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Atenda aos requisitos de conformidade em ofertas</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>96
+Ação necessária: Informações importantes sobre suas ofertas
+ Estamos entrando em contato porque você publicou produtos que exigem o envio de documentos para verificação de conformidade.
+ As ofertas estão sem os documentos de conformidade necessários
+ Olá,
+ Estamos entrando em contato porque você publicou produtos que exigem o envio de documentos para verificação de conformidade. Clique em Revisar requisitos de conformidade abaixo para acessar a lista de produtos afetados e enviar os documentos necessários. Se você não enviar os documentos até o prazo indicado para cada produto nesse link, poderemos excluir as ofertas afetadas.
+ Revisar requisitos de conformidade
+ A tabela abaixo contém uma amostra das ofertas afetadas. Clique em Revisar requisitos de conformidade para consultar todas as suas ofertas afetadas.
+ SKU ASIN Status da oferta 7N-0PZT-LEBX B0FCDRNTT8 Em risco de remoção
+ Por que isso está acontecendo?
+Essa exigência ajuda a garantir que os produtos estejam em conformidade com as leis locais e sejam seguros para os clientes.
+ Como faço para continuar vendendo os produtos afetados?
+Clique em Revisar requisitos de conformidade para obter mais informações sobre os documento</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 8 Mar 2026 12:42:53 +0000</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.nl&gt;</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Wijziging in geschiktheid voor opties voor premiumverzending</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>96
+Wijziging in geschiktheid voor opties voor premiumverzending
+Weihai EU,
+Je komt momenteel niet in aanmerking om Premium-verzendopties aan te bieden voor door verkoper afgehandelde bestellingen. Je status is gewijzigd omdat we hebben gemerkt dat een of meer van je prestatiestatistieken onder de programmavereisten zijn gedaald.
+Je kunt je prestatiestatistieken bekijken met behulp van de widget Geschiktheid voor Premium-verzending . Als je weer in aanmerking wilt komen voor Premium-verzendopties, moet je een actieplan indienen door op deze e-mail te reageren of te schrijven naar op-pso-vtr-appeals@amazon.nl .
+Om Premium-verzendopties aan te bieden, moeten verkopers het volgende doen:
+- 90 dagen of langer verkopen op Amazon
+- Tien of meer bestellingen in de laatste 30 dagen hebben verzonden
+- Een percentage tijdige bezorgingen van 97% of hoger behouden voor alle bestellingen met Premium-verzendopties
+- Een percentage geldige trackingnummers van 100% behouden voor alle bestellingen met Premium-verzendopties
+- Een annuleringspercentage van 0,5% of minder behouden voor alle bestellingen met Premium-verzendopties
+Verzonden door Amazon-bestellingen (FBA) worden niet beïnvloed door deze s</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 12:16:06 +0000</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.se&gt;</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Behörighet att ändra alternativ för Premiumfrakt</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>96
+Behörighet att ändra alternativ för Premiumfrakt
+Weihai EU,
+Du är för närvarande inte berättigad att erbjuda Premiumfrakt-alternativ för dina beställningar levererade av säljare. Din status har ändrats eftersom vi har märkt att en eller flera av dina resultatmätningar har sjunkit under gränsen för programkraven.
+Du kan granska dina resultatmätningar med widgeten Berättigande för premiumfrakt . För att återställa behörigheten för alternativen för Premiumfrakt skickar du in en handlingsplan genom att svara på det här e-postmeddelandet eller skriva till op-pso-vtr-appeals@amazon.se .
+För att kunna erbjuda alternativ för Premiumfrakt måste säljare:
+- Ha sålt på Amazon i 90 dagar eller mer
+- Skickat tio eller fler beställningar de senaste 30 dagarna
+- Upprätthålla en leveranshastighet på 97 % eller högre för alla beställningar med alternativ för beställningar med Premiumfrakt
+- Upprätthålla en giltig spårningsfrekvens på 100 % för alla beställningar med Premiumfrakt
+- Upprätthålla en annulleringsgrad på 0,5 % eller mindre för alla beställningar med Premiumfrakt
+Fraktas från Amazon-beställningar (FBA) påverkas inte av denna statusändring.
+ Observera : Skicka alla öppna beställningar m</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 6 Mar 2026 05:10:16 +0000</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Premium Shipping option eligibility suspended due to program
+ requirement violation</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>96
+Premium Shipping option eligibility suspended due to program requirement violation
+Weihai EU,
+You are currently not eligible to offer Premium Shipping options for your seller-fulfilled orders. Your status has changed because we noticed that one or more of your performance metrics has fallen below the program requirements.
+You can review your performance metrics using the Premium Shipping Eligibility widget . To restore eligibility for Premium Shipping Options, please submit a Plan of Action by replying to this email or writing to op-pso-vtr-appeals@amazon.com .
+To offer Premium Shipping options, sellers are required to:
+- Have sold on Amazon for 90 days or more
+- Ship ten or more orders in the last 30 days
+- Maintain an on-time delivery rate of 97% or greater for all Premium Shipping option orders
+- Maintain a valid tracking rate of 100% for all Premium Shipping option orders
+- Maintain a cancellation rate of 0.5% or less for all Premium Shipping option orders
+Fulfillment by Amazon (FBA) orders are not affected by this status change.
+ Note : Please ship any open Premium Shipping option orders with the ship option selected when the order was placed.
+Thank you for selling on Amazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 5 Mar 2026 20:28:12 +0000</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Notifications Amazon Seller Central (Ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Répondez aux exigences de conformité pour vos mises en vente</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>96
+Action requise : informations importantes concernant vos offres
+ Nous vous contactons car vous avez répertorié des produits qui nécessitent que vous soumettiez des documents de conformité.
+ Vos produits mis en vente ne disposent pas des documents de conformité requis
+ Bonjour,
+ Nous vous contactons car vous avez mis en vente des produits pour lesquels des documents de conformité sont requis. Cliquez sur Afficher les exigences de conformité ci-dessous pour consulter la liste des produits concernés et soumettre les documents de conformité nécessaires. Si vous ne soumettez pas ces documents avant la date limite indiquée pour chaque produit dans ce lien, nous pourrions supprimer les mises en vente concernées.
+ Afficher les exigences de conformité
+ Le tableau ci-dessous présente un échantillon de vos produits mis en vente concernés. Cliquez sur Afficher les exigences de conformité pour consulter l’ensemble de vos mises en vente concernées.
+ SKU ASIN État de la mise en vente WHEUSGMH81901 B0DD7R3PPG Présentant un risque de prélèvement
+ Pourquoi cela se produit-il ?
+Cette exigence nous aide à garantir que les produits respectent la législation locale et ne présentent pas de danger pour</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 1 Mar 2026 00:16:30 +0000</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>View your US Q1-2026 CSBA fee rate</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>96
+ (Important) CSBA US Fee rate for Q1-2026
+ Review your updated Customer Service by Amazon fee rate and metrics
+ Hello,
+ This is your quarterly update regarding Customer Service by Amazon (CSBA) fees.
+ Your CSBA fee rate for Q1-2026 (Jan 1, 2026 through Mar 31, 2026) will be based on your performance metrics from Q4-2025 (Oct 1, 2025 through Dec 25, 2025). To learn more about program fees, go to Customer Service by Amazon fees .
+ Fee tier &amp; rate
+ Q4-2025 contacts
+ 0
+ Q4-2025 self-fulfilled shipped units
+ 0
+ Q4-2025 contacts per unit (CPU¹)
+ N/A%
+ Q1-2026 fee rate² ($ per self-fulfilled shipped unit)
+ $0.00
+ ¹ Contacts per unit (CPU) = CSBA contacts / self-fulfilled shipped units
+ ² Your fee rate for the previous quarter was $0.00.
+ CSBA Insights Dashboard
+ Get the most out of Customer Service by Amazon
+ Use the CSBA Insights dashboard in Seller Central to:
+- Review customer service contacts handled by Amazon
+- Find ways to improve customer experience
+- Reduce contact and return rates
+ Follow these practices to prevent customer confusion and minimize your workload:
+- Monitor the Response Needed inbox within the Buyer-Seller Messaging Service . In the rare case that we need your he</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 28 Feb 2026 02:10:48 +0000</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>[Action Required] Provide additional information within 60 days to
+ avoid account deactivation under European VAT registration requirements</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai EU,
+ We need you to provide additional information in order to comply with Amazon’s European Value Added Tax (VAT) registration requirements.
+ Why is this happening?
+ According to Amazon’s European VAT registration requirements you must provide us with a valid VAT Registration Number (‘VRN’) for all the countries in which we believe you have a VAT registration obligation or confirmation of the Union One-Stop Shop (OSS) status for your home country.
+ We identified VAT registration requirements for your account in the European Union, the United Kingdom, Norway, and Switzerland in which you have VAT obligation. Specifically, action may be required for the following:
+ Poland
+ To learn more, go to the European Value Added Tax Information Help page.
+ How do I avoid account deactivation?
+ To avoid account deactivation, within the next 60 days visit the Priority Actions section on your Account Health page . From there, you will be able to:
+- Verify your existing information for listed countries
+- Submit VAT information through Business Information and Tax Setting portals
+- Submit required documentation for extension or exemption requests
+ What happens if I don’t provide th</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 28 Feb 2026 02:06:07 +0000</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>[Action required] Provide additional information within 60 days to
+ avoid account deactivation under European VAT registration requirements</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai EU,
+ We need you to provide additional information in order to comply with Amazon’s European Value Added Tax (VAT) registration requirements.
+ Why is this happening?
+ According to Amazon’s European VAT registration requirements, you must provide us with a valid VAT registration number (“VRN”) for all the countries in which we believe you have a VAT registration obligation, or confirmation of the Union One-Stop Shop (OSS) status for your home country.
+ We identified VAT registration requirements for your account in the European Union, the United Kingdom, Norway and Switzerland in which you have Value Added Tax (VAT) obligation. Specifically, action may be required for the following:
+ Poland
+ To learn more, go to the European Value Added Tax information help page.
+ How do I avoid account deactivation?
+ To avoid account deactivation, within the next 60 days visit the Priority actions section on your Account Health page . From there, you will be able to:
+- Verify your existing information for listed countries
+- Submit Value Added Tax (VAT) information through business information and tax setting portals
+- Submit required documentation for extension or exemption request</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 26 Feb 2026 01:35:07 +0000</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Upload proof of insurance and explore new best practices guide</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Upload proof of commercial liability insurance by March 30, 2026. Review our new best practices guide for mainland China-based sellers to help you avoid common coverage gaps and policy issues.
+ Hello,
+ To sell on Amazon, you must obtain and maintain a valid commercial liability insurance policy for all of your products once your gross proceeds in sales exceed $10,000 in any month, or if requested by us, as outlined in Section 9 of the Amazon Services Business Solutions Agreement .
+ We request that you take the following steps to provide proof of commercial liability insurance by March 30, 2026:
+- Request a Certificate of Insurance from your insurance provider that details your coverage, including policy limits, exclusions, and deductibles.
+- Submit your Certificate of Insurance via Business Insurance . To help you navigate this process, we’ve created the Commercial Liability Insurance Best Practices for Sellers Based in Mainland China help page. It addresses common policy issues that can lead to claims denials like coverage gaps or invalid coverage dates. It also includes information and best practices on:
+- Deductible advancement
+- Coverage continuity and sunset clauses
+- US c</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/important_mails_2026-03-20.xlsx
+++ b/important_mails_2026-03-20.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
+          <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -510,11 +510,64 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
+          <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated removals of unfulfillable inventory
+ Required removals: First notification
+ Required removals: First notification
+ Hello,
+Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-04-02 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
+Unsellable products:
+- FNSKU: X002A05YW5 Quantity: 1
+ Why is this happening?
+This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
+We leveraged a combination of automated means to identify this issue and make this decision.
+ How do I address this?
+Follow these steps to manage your unsellable inventory:
+- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
+- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
+ To avoid future manual inventory removal orders, set up Automated Unfulfillable Removals function in your FBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Disposal order created for unsellable FBA inventory</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -538,39 +591,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -593,39 +646,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -639,39 +692,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -688,39 +741,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -739,39 +792,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -789,39 +842,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -837,39 +890,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -885,39 +938,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -935,39 +988,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -984,39 +1037,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -1040,39 +1093,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1087,39 +1140,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -1135,39 +1188,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -1184,40 +1237,40 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -1233,39 +1286,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -1282,61 +1335,6 @@
  Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
  Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
  SPC-EUAmazon-1794404611296645</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated Removals of Unfulfillable Inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Hello,
-You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
- Why is this happening?
-This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
- Removal order ID:
-- rJ8tXXz1/k
- Unsellable Products:
-- FNSKU: X002A05YW5 Quantity: 1
- For more information about the disposal order process, see Remove inventory from a fulfilment centre .
- To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
- The Fulfilment by Amazon Team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferen</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7462,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
+          <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -7474,11 +7472,66 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Create FBA removal order by 2026-03-26</t>
+          <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated Removals of Unfulfillable Inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Hello,
+You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
+ Why is this happening?
+This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
+ Removal order ID:
+- rJ8tXXz1/k
+ Unsellable Products:
+- FNSKU: X002A05YW5 Quantity: 1
+ For more information about the disposal order process, see Remove inventory from a fulfilment centre .
+ To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
+ The Fulfilment by Amazon Team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferen</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Create FBA removal order by 2026-03-26</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7500,39 +7553,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:58:29 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7555,39 +7608,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:29:25 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7610,39 +7663,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 07:49:31 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>New removal fees for KSA apply starting March 30</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
  Effective March 30, 2026, removal fees will apply in the Kingdom of Saudi Arabia (KSA) for removals you initiate.
@@ -7668,39 +7721,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 13:57:30 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-12</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7722,39 +7775,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 12:08:33 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7778,39 +7831,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 13:32:21 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Stranded SKUs scheduled for automatic removal</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
 Stranded SKUs scheduled for automatic removal
@@ -7822,39 +7875,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Feb 2026 13:43:58 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7878,39 +7931,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Feb 2026 13:32:50 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-05</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7931,39 +7984,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -7977,39 +8030,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Atenda aos requisitos de conformidade em ofertas</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
 Ação necessária: Informações importantes sobre suas ofertas
@@ -8027,39 +8080,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 12:42:53 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.nl&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Wijziging in geschiktheid voor opties voor premiumverzending</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
 Wijziging in geschiktheid voor opties voor premiumverzending
@@ -8076,39 +8129,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 12:16:06 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Behörighet att ändra alternativ för Premiumfrakt</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
 Behörighet att ändra alternativ för Premiumfrakt
@@ -8126,40 +8179,40 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 05:10:16 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Premium Shipping option eligibility suspended due to program
  requirement violation</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
 Premium Shipping option eligibility suspended due to program requirement violation
@@ -8178,39 +8231,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:12 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (Ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Répondez aux exigences de conformité pour vos mises en vente</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
 Action requise : informations importantes concernant vos offres
@@ -8226,39 +8279,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Sun, 1 Mar 2026 00:16:30 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>View your US Q1-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q1-2026
@@ -8288,40 +8341,40 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:10:48 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8340,40 +8393,40 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:06:07 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8391,39 +8444,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 01:35:07 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Upload proof of insurance and explore new best practices guide</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
  Upload proof of commercial liability insurance by March 30, 2026. Review our new best practices guide for mainland China-based sellers to help you avoid common coverage gaps and policy issues.

--- a/important_mails_2026-03-20.xlsx
+++ b/important_mails_2026-03-20.xlsx
@@ -795,7 +795,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -810,71 +810,21 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
+          <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Submit product safety documentation to reactivate listings</t>
+          <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
- For step-by-step instru</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -890,39 +840,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -938,39 +888,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -988,39 +938,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1037,39 +987,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -1093,39 +1043,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1140,39 +1090,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -1188,39 +1138,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -1237,40 +1187,40 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -1286,92 +1236,40 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>96
-Amazon UAE
- Amazon Announcement
- Hello,
- We previously communicated that Fulfillment by Amazon (FBA) removal fees would be introduced in the UAE and Saudi Arabia on March 30, 2026.
-Due to the developing situation in the Middle East, we will not apply FBA removal fees in UAE and Saudi Arabia until further notice . No fees will apply for FBA removal orders initiated by you or Amazon.
-We will notify you of any future change to this policy in advance.
-The Amazon Services team
-- .
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
- SPC-EUAmazon-1794404611296645</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -1390,40 +1288,40 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -1441,40 +1339,40 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -1490,39 +1388,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1542,39 +1440,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -1588,39 +1486,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1640,39 +1538,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:16:27 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1693,39 +1591,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 04:02:47 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (uih6sNeVfd)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1745,39 +1643,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 20:32:33 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (DjHMcVqBnq)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1797,40 +1695,40 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:54:28 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 29.08 in an attempt to settle your Amazon.ca seller account balance.
@@ -1846,39 +1744,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 06:14:30 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (X8HTY1kPjb)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1904,39 +1802,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Feb 2026 17:52:28 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1957,39 +1855,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Feb 2026 21:45:54 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (SOu11lTFx5)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2015,39 +1913,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Feb 2026 03:59:48 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2063,39 +1961,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Wed, 18 Feb 2026 09:45:35 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2111,39 +2009,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
@@ -2158,39 +2056,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2214,39 +2112,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 15:16:36 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 30.46. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2260,39 +2158,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 14:57:34 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Negatieve saldoaanpassing voor al je accounts</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2309,39 +2207,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 13:38:27 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2361,39 +2259,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 15:38:46 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2410,39 +2308,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 16:06:24 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2466,39 +2364,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 14:48:41 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2518,39 +2416,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 14:12:31 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2570,39 +2468,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Feb 2026 14:54:33 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -2618,39 +2516,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Feb 2026 13:38:32 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2670,39 +2568,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Feb 2026 13:37:02 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2722,39 +2620,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Feb 2026 15:49:30 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europa &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Ajuste de saldo negativo en tus cuentas de Vender en Amazon</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2778,39 +2676,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Feb 2026 12:00:21 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2830,39 +2728,89 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
+ For step-by-step instru</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -2884,39 +2832,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -2939,39 +2887,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:20 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2990,39 +2938,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:09:14 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3041,39 +2989,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:43 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3093,39 +3041,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:31 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3145,39 +3093,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Vereisten voor naleving van je productvermeldingen aanpakken</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 Actie vereist: Belangrijke informatie over je productvermeldingen
@@ -3195,39 +3143,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3245,39 +3193,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Rispondi ai requisiti di conformità per le tue offerte</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 Azione richiesta: Informazioni importanti sulle sue offerte
@@ -3295,39 +3243,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:29 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3346,39 +3294,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 05:28:30 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3396,40 +3344,40 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 08:54:27 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3447,39 +3395,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 05:31:26 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3497,39 +3445,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 21:23:05 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -3547,39 +3495,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:18:58 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3594,39 +3542,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 09:56:14 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3642,39 +3590,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 05:24:39 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3692,39 +3640,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 21:13:50 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -3742,39 +3690,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:49 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3792,40 +3740,40 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 11:03:26 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 26/04/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 26/04/2026 to avoid shipping restrictions
@@ -3844,39 +3792,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 05:20:21 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3894,39 +3842,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Feb 2026 16:07:02 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Submit Product Safety Law compliance information for Saudi Arabia</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  You can now submit PSL compliance information through the listing workflow and Manage All Inventory.
@@ -3948,39 +3896,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 20:18:57 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3998,39 +3946,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 17:12:51 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4049,39 +3997,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 17:10:23 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4100,39 +4048,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 16:27:54 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Notificaciones automáticas de Amazon Seller Central (favor de no responder a este mensaje) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento para los listados</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 Acción requerida: Información importante sobre tus listados de productos
@@ -4149,39 +4097,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Wed, 18 Feb 2026 20:09:07 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4200,39 +4148,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Feb 2026 16:10:02 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -4247,6 +4195,58 @@
 -
  If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
  For step-by-step instru</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>96
+Amazon UAE
+ Amazon Announcement
+ Hello,
+ We previously communicated that Fulfillment by Amazon (FBA) removal fees would be introduced in the UAE and Saudi Arabia on March 30, 2026.
+Due to the developing situation in the Middle East, we will not apply FBA removal fees in UAE and Saudi Arabia until further notice . No fees will apply for FBA removal orders initiated by you or Amazon.
+We will notify you of any future change to this policy in advance.
+The Amazon Services team
+- .
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+ SPC-EUAmazon-1794404611296645</t>
         </is>
       </c>
     </row>

--- a/important_mails_2026-03-20.xlsx
+++ b/important_mails_2026-03-20.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H161"/>
+  <dimension ref="A1:H160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>货件/库存类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -500,21 +500,69 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
+          <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+          <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Create FBA removal order by 2026-04-02</t>
+          <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
+We recommend you to submit the required documents to un-suppress your ASIN and activate your listings.
+Here is a sample of your suppressed ASINs:
+B0F13M1H6F, B0D97JS8WD
+You can download the full list of your suppressed ASINs from the following path “Catalog” &gt;&gt; “Complete your drafts” &gt;&gt; “Completed with Issues” &gt;&gt; “Detail page removed”
+https://sellercentral.amazon.ca/fixyourproducts/drafts
+To upload the required documents or to appeal in-order to un-suppress the ASINs, please follow this path  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
+ https://sellercentral.amazon.ca/performance/account/health/compliance-request
+If you need further help, please raise a case via contact us. - https://sellercentral.amazon.ca/cu/contact-us?ref=xx_ContactUs_xxxx_helphub
+If you are not the correct point of contact, please re-direct this email to the correct point of contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Create FBA removal order by 2026-04-02</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -535,39 +583,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -591,39 +639,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -646,39 +694,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -692,39 +740,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -741,39 +789,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -792,39 +840,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -840,39 +888,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -888,39 +936,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -938,39 +986,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -987,39 +1035,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -1043,39 +1091,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1090,39 +1138,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -1138,39 +1186,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -1187,40 +1235,40 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -1236,40 +1284,40 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -1288,40 +1336,40 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -1339,40 +1387,40 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -1388,39 +1436,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1440,39 +1488,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -1486,39 +1534,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1538,39 +1586,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:16:27 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1591,39 +1639,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 04:02:47 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (uih6sNeVfd)</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1643,39 +1691,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 20:32:33 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (DjHMcVqBnq)</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1695,40 +1743,40 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:54:28 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 29.08 in an attempt to settle your Amazon.ca seller account balance.
@@ -1744,39 +1792,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 06:14:30 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (X8HTY1kPjb)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1802,39 +1850,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Feb 2026 17:52:28 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1855,39 +1903,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Feb 2026 21:45:54 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (SOu11lTFx5)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1913,39 +1961,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Feb 2026 03:59:48 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1958,54 +2006,6 @@
 - In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
 - To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
 -</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 18 Feb 2026 09:45:35 +0000</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfillment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfillment center. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.com/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.com/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
-- T</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4166,71 +4166,21 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 16:10:02 +0000</t>
+          <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Submit product safety documentation to reactivate listings</t>
+          <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
- For step-by-step instru</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -4250,39 +4200,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -4298,40 +4248,40 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4347,39 +4297,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>春季促销日 2026：最后提报您促销活动的机会</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -4396,39 +4346,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 15:38:05 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 2/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -4447,39 +4397,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 11:10:45 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -4497,39 +4447,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Sat, 7 Mar 2026 01:02:00 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 2/2026</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 2/2026 is now available in your Seller Central Account.
@@ -4541,39 +4491,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:28:03 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4585,39 +4535,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:16:57 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -4629,39 +4579,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:10:12 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4673,39 +4623,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 22:15:50 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4717,39 +4667,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 21:01:28 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 2 2026</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 2 i rok 2026.
@@ -4761,39 +4711,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:56:07 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4805,39 +4755,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -4849,39 +4799,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:57 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -4899,39 +4849,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:26 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  尊敬的 Weihai EU：
@@ -4974,39 +4924,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:57 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -5023,40 +4973,40 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:27 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -5074,39 +5024,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:12:48 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -5124,39 +5074,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5168,39 +5118,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:17 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5212,39 +5162,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:06 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 2/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5263,39 +5213,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:35:00 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5307,39 +5257,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:32:44 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5351,39 +5301,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:24:20 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5395,39 +5345,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:55:05 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5439,39 +5389,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:24:37 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5483,39 +5433,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:58:56 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5527,39 +5477,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:48:50 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5571,39 +5521,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:11:22 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5615,39 +5565,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:54:03 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5659,40 +5609,40 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:44:53 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 2/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5711,39 +5661,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:38:12 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5755,40 +5705,40 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:28:10 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>La tua Fattura Elettronica Amazon Marketing Service Amazon.it per
  2/2026</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Gentile Shen zhen shi wei hai zhong xin ke ji you xian,
 Ti informiamo che la tua Fattura Elettronica Amazon Marketing Service per il mese di 2/2026 è ora disponibile sul tuo account di Seller Central.
@@ -5800,39 +5750,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:09:11 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5844,39 +5794,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:32:33 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Fulfillment by Amazon Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) لتاجر Fulfilment by Amazon الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5895,39 +5845,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:13:19 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5939,39 +5889,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:56:47 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5990,39 +5940,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:29:22 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 2 2026</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 2 i rok 2026.
@@ -6034,39 +5984,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 11:10:20 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6082,40 +6032,40 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:11:42 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6133,39 +6083,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:08:11 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -6183,39 +6133,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:32 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Spełnij wymogi zgodności dotyczące Twoich ofert</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 Wymagane działanie: Ważna informacja dotycząca Twoich ofert produktów
@@ -6231,39 +6181,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:29 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento de tus listings</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
 Toma medidas: Información importante sobre tus listings de producto
@@ -6281,39 +6231,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:47 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -6354,39 +6304,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:22 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -6404,40 +6354,40 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:12:51 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -6455,39 +6405,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:28 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6504,39 +6454,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:09:31 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -6554,39 +6504,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 11:10:25 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6604,39 +6554,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 00:58:56 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>最后机会：请在3月9日前提报春季促销日的促销</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>3月9日前提报春季促销日促销
 尊敬的卖家，
@@ -6651,39 +6601,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 21:40:34 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6697,39 +6647,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 11:10:30 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6745,39 +6695,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:13:10 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 60 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -6793,39 +6743,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:09:55 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 60 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6842,40 +6792,40 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:07:47 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 60 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6891,39 +6841,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 18:30:15 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para marzo</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para marzo
@@ -6952,39 +6902,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:58 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -7001,40 +6951,40 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:56 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -7051,39 +7001,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:35 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7098,40 +7048,40 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:40 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -7146,39 +7096,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:31 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -7193,39 +7143,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:23 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -7240,39 +7190,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 15:01:07 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7287,39 +7237,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 10:49:26 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -7347,39 +7297,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 17:09:03 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Envía documentos de cumplimiento normativo del producto para evitar que se retiren los listados</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Envía documentos de cumplimiento normativo del producto para evitar que se retiren los listados
@@ -7393,39 +7343,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Feb 2026 04:17:16 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7444,39 +7394,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7499,39 +7449,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7553,39 +7503,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:58:29 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7608,39 +7558,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:29:25 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7663,39 +7613,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 07:49:31 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>New removal fees for KSA apply starting March 30</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
  Effective March 30, 2026, removal fees will apply in the Kingdom of Saudi Arabia (KSA) for removals you initiate.
@@ -7721,39 +7671,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 13:57:30 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-12</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7775,39 +7725,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 12:08:33 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7831,39 +7781,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 13:32:21 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Stranded SKUs scheduled for automatic removal</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
 Stranded SKUs scheduled for automatic removal
@@ -7875,39 +7825,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Feb 2026 13:43:58 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7931,39 +7881,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Feb 2026 13:32:50 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-05</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7984,39 +7934,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -8030,39 +7980,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Atenda aos requisitos de conformidade em ofertas</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
 Ação necessária: Informações importantes sobre suas ofertas
@@ -8080,39 +8030,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 12:42:53 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.nl&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Wijziging in geschiktheid voor opties voor premiumverzending</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
 Wijziging in geschiktheid voor opties voor premiumverzending
@@ -8129,39 +8079,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 12:16:06 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Behörighet att ändra alternativ för Premiumfrakt</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
 Behörighet att ändra alternativ för Premiumfrakt
@@ -8179,40 +8129,40 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 05:10:16 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Premium Shipping option eligibility suspended due to program
  requirement violation</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
 Premium Shipping option eligibility suspended due to program requirement violation
@@ -8231,39 +8181,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:12 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (Ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Répondez aux exigences de conformité pour vos mises en vente</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
 Action requise : informations importantes concernant vos offres
@@ -8279,39 +8229,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Sun, 1 Mar 2026 00:16:30 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>View your US Q1-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q1-2026
@@ -8341,40 +8291,40 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:10:48 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8393,40 +8343,40 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:06:07 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8444,39 +8394,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 01:35:07 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Upload proof of insurance and explore new best practices guide</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  Upload proof of commercial liability insurance by March 30, 2026. Review our new best practices guide for mainland China-based sellers to help you avoid common coverage gaps and policy issues.
